--- a/02_Inputs/Data/Charts/Module 2 - Datasets for Charts.xlsx
+++ b/02_Inputs/Data/Charts/Module 2 - Datasets for Charts.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://undp.sharepoint.com/sites/SEHCoreTeam/Shared Documents/General/04. Sustainable Energy Academy/SEA Charts and Infographics/SEA - Charts/Datasets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="944" documentId="11_C37B7BF874E036F1B873F16424B654186DDE5F8D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{47D48480-ECAA-4BBA-AABA-C5C31AFB3DFD}"/>
+  <xr:revisionPtr revIDLastSave="947" documentId="11_C37B7BF874E036F1B873F16424B654186DDE5F8D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{23D66403-AD8F-445C-9F09-88C9908CC680}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="8" activeTab="24" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="16" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="M2_C2_47_1" sheetId="16" r:id="rId1"/>
@@ -28,8 +28,8 @@
     <sheet name="M2_C2_54_3" sheetId="25" r:id="rId13"/>
     <sheet name="M2_C2_55" sheetId="5" r:id="rId14"/>
     <sheet name="M2_C2_56" sheetId="6" r:id="rId15"/>
-    <sheet name="M2_C_58_1" sheetId="7" r:id="rId16"/>
-    <sheet name="M2_C_58_2" sheetId="29" r:id="rId17"/>
+    <sheet name="M2_C2_58_1" sheetId="7" r:id="rId16"/>
+    <sheet name="M2_C2_58_2" sheetId="29" r:id="rId17"/>
     <sheet name="M2_C2_59" sheetId="8" r:id="rId18"/>
     <sheet name="M2_C2_60" sheetId="12" r:id="rId19"/>
     <sheet name="M2_C2_61" sheetId="11" r:id="rId20"/>
@@ -1147,217 +1147,217 @@
     <t>Electricity</t>
   </si>
   <si>
+    <t>Entity</t>
+  </si>
+  <si>
+    <t>Cold deaths</t>
+  </si>
+  <si>
+    <t>Heat deaths</t>
+  </si>
+  <si>
+    <t>Africa</t>
+  </si>
+  <si>
+    <t>Americas</t>
+  </si>
+  <si>
+    <t>Asia</t>
+  </si>
+  <si>
+    <t>Australia and New Zealand</t>
+  </si>
+  <si>
+    <t>Central Asia</t>
+  </si>
+  <si>
+    <t>East Asia</t>
+  </si>
+  <si>
+    <t>Eastern Europe</t>
+  </si>
+  <si>
+    <t>Europe</t>
+  </si>
+  <si>
+    <t>North Africa</t>
+  </si>
+  <si>
+    <t>North America</t>
+  </si>
+  <si>
+    <t>Northern Europe</t>
+  </si>
+  <si>
+    <t>South Asia</t>
+  </si>
+  <si>
+    <t>South-east Asia</t>
+  </si>
+  <si>
+    <t>Southern Europe</t>
+  </si>
+  <si>
+    <t>West Asia</t>
+  </si>
+  <si>
+    <t>Western Europe</t>
+  </si>
+  <si>
+    <t>Population needing cooling (from hot climates)</t>
+  </si>
+  <si>
+    <t>Additional population needing cooling</t>
+  </si>
+  <si>
+    <t>AC penetration in 2000</t>
+  </si>
+  <si>
+    <t>AC penetration in 2022</t>
+  </si>
+  <si>
+    <t>Asia Pacific</t>
+  </si>
+  <si>
+    <t>Central and South America</t>
+  </si>
+  <si>
+    <t>Eurasia</t>
+  </si>
+  <si>
+    <t>Middle East</t>
+  </si>
+  <si>
+    <t>World average</t>
+  </si>
+  <si>
+    <t>Rural poor</t>
+  </si>
+  <si>
+    <t>Urban poor</t>
+  </si>
+  <si>
+    <t>Total at high risk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">India </t>
+  </si>
+  <si>
+    <t xml:space="preserve">China </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nigeria </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pakistan </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bangladesh </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brazil </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Indonesia </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mozambique </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Angola </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uganda </t>
+  </si>
+  <si>
+    <t>Proportion of total population at high risk</t>
+  </si>
+  <si>
+    <t>Share of women in total population at high risk</t>
+  </si>
+  <si>
+    <t>Unspecified countries</t>
+  </si>
+  <si>
+    <t>LDCs (USD bn)</t>
+  </si>
+  <si>
+    <t>LLDCs (USD bn)</t>
+  </si>
+  <si>
+    <t>SIDS (USD bn)</t>
+  </si>
+  <si>
+    <t>Scenario</t>
+  </si>
+  <si>
+    <t>Grid (USD bn)</t>
+  </si>
+  <si>
+    <t>Mini-grid (USD bn)</t>
+  </si>
+  <si>
+    <t>Stand-alone (USD bn)</t>
+  </si>
+  <si>
+    <t>Total (USD bn)</t>
+  </si>
+  <si>
+    <t>Low Demand</t>
+  </si>
+  <si>
+    <t>Bottom-Up</t>
+  </si>
+  <si>
+    <t>High Demand</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Population</t>
+  </si>
+  <si>
+    <t>Natural gas</t>
+  </si>
+  <si>
+    <t>1.68 billion</t>
+  </si>
+  <si>
+    <t>LPG</t>
+  </si>
+  <si>
+    <t>1.48 billion</t>
+  </si>
+  <si>
+    <t>890 million</t>
+  </si>
+  <si>
+    <t>Biogas &amp; ethanol</t>
+  </si>
+  <si>
+    <t>232 million</t>
+  </si>
+  <si>
+    <t>People without access</t>
+  </si>
+  <si>
+    <t>2 billion</t>
+  </si>
+  <si>
+    <t>Solution</t>
+  </si>
+  <si>
+    <t>Share (%)</t>
+  </si>
+  <si>
+    <t>Improved stoves</t>
+  </si>
+  <si>
+    <t>Sp</t>
+  </si>
+  <si>
     <t>Period</t>
-  </si>
-  <si>
-    <t>Entity</t>
-  </si>
-  <si>
-    <t>Cold deaths</t>
-  </si>
-  <si>
-    <t>Heat deaths</t>
-  </si>
-  <si>
-    <t>Africa</t>
-  </si>
-  <si>
-    <t>Americas</t>
-  </si>
-  <si>
-    <t>Asia</t>
-  </si>
-  <si>
-    <t>Australia and New Zealand</t>
-  </si>
-  <si>
-    <t>Central Asia</t>
-  </si>
-  <si>
-    <t>East Asia</t>
-  </si>
-  <si>
-    <t>Eastern Europe</t>
-  </si>
-  <si>
-    <t>Europe</t>
-  </si>
-  <si>
-    <t>North Africa</t>
-  </si>
-  <si>
-    <t>North America</t>
-  </si>
-  <si>
-    <t>Northern Europe</t>
-  </si>
-  <si>
-    <t>South Asia</t>
-  </si>
-  <si>
-    <t>South-east Asia</t>
-  </si>
-  <si>
-    <t>Southern Europe</t>
-  </si>
-  <si>
-    <t>West Asia</t>
-  </si>
-  <si>
-    <t>Western Europe</t>
-  </si>
-  <si>
-    <t>Population needing cooling (from hot climates)</t>
-  </si>
-  <si>
-    <t>Additional population needing cooling</t>
-  </si>
-  <si>
-    <t>AC penetration in 2000</t>
-  </si>
-  <si>
-    <t>AC penetration in 2022</t>
-  </si>
-  <si>
-    <t>Asia Pacific</t>
-  </si>
-  <si>
-    <t>Central and South America</t>
-  </si>
-  <si>
-    <t>Eurasia</t>
-  </si>
-  <si>
-    <t>Middle East</t>
-  </si>
-  <si>
-    <t>World average</t>
-  </si>
-  <si>
-    <t>Rural poor</t>
-  </si>
-  <si>
-    <t>Urban poor</t>
-  </si>
-  <si>
-    <t>Total at high risk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">India </t>
-  </si>
-  <si>
-    <t xml:space="preserve">China </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nigeria </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pakistan </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bangladesh </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brazil </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Indonesia </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mozambique </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Angola </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Uganda </t>
-  </si>
-  <si>
-    <t>Proportion of total population at high risk</t>
-  </si>
-  <si>
-    <t>Share of women in total population at high risk</t>
-  </si>
-  <si>
-    <t>Unspecified countries</t>
-  </si>
-  <si>
-    <t>LDCs (USD bn)</t>
-  </si>
-  <si>
-    <t>LLDCs (USD bn)</t>
-  </si>
-  <si>
-    <t>SIDS (USD bn)</t>
-  </si>
-  <si>
-    <t>Scenario</t>
-  </si>
-  <si>
-    <t>Grid (USD bn)</t>
-  </si>
-  <si>
-    <t>Mini-grid (USD bn)</t>
-  </si>
-  <si>
-    <t>Stand-alone (USD bn)</t>
-  </si>
-  <si>
-    <t>Total (USD bn)</t>
-  </si>
-  <si>
-    <t>Low Demand</t>
-  </si>
-  <si>
-    <t>Bottom-Up</t>
-  </si>
-  <si>
-    <t>High Demand</t>
-  </si>
-  <si>
-    <t>Category</t>
-  </si>
-  <si>
-    <t>Population</t>
-  </si>
-  <si>
-    <t>Natural gas</t>
-  </si>
-  <si>
-    <t>1.68 billion</t>
-  </si>
-  <si>
-    <t>LPG</t>
-  </si>
-  <si>
-    <t>1.48 billion</t>
-  </si>
-  <si>
-    <t>890 million</t>
-  </si>
-  <si>
-    <t>Biogas &amp; ethanol</t>
-  </si>
-  <si>
-    <t>232 million</t>
-  </si>
-  <si>
-    <t>People without access</t>
-  </si>
-  <si>
-    <t>2 billion</t>
-  </si>
-  <si>
-    <t>Solution</t>
-  </si>
-  <si>
-    <t>Share (%)</t>
-  </si>
-  <si>
-    <t>Improved stoves</t>
-  </si>
-  <si>
-    <t>Sp</t>
   </si>
   <si>
     <t>Rest of World</t>
@@ -6478,7 +6478,7 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="34" t="s">
-        <v>358</v>
+        <v>0</v>
       </c>
       <c r="B1" s="34" t="s">
         <v>356</v>
@@ -9003,21 +9003,21 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="28" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B1" s="28" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="28" t="s">
+        <v>359</v>
+      </c>
+      <c r="D1" s="28" t="s">
         <v>360</v>
-      </c>
-      <c r="D1" s="28" t="s">
-        <v>361</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="28" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B2" s="28">
         <v>2019</v>
@@ -9031,7 +9031,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="28" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B3" s="28">
         <v>2019</v>
@@ -9045,7 +9045,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="28" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B4" s="28">
         <v>2019</v>
@@ -9059,7 +9059,7 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="28" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B5" s="28">
         <v>2019</v>
@@ -9073,7 +9073,7 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="28" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B6" s="28">
         <v>2019</v>
@@ -9087,7 +9087,7 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="28" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B7" s="28">
         <v>2019</v>
@@ -9101,7 +9101,7 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="28" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B8" s="28">
         <v>2019</v>
@@ -9115,7 +9115,7 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="28" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B9" s="28">
         <v>2019</v>
@@ -9143,7 +9143,7 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="28" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B11" s="28">
         <v>2019</v>
@@ -9157,7 +9157,7 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="28" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B12" s="28">
         <v>2019</v>
@@ -9171,7 +9171,7 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="28" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B13" s="28">
         <v>2019</v>
@@ -9199,7 +9199,7 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="28" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B15" s="28">
         <v>2019</v>
@@ -9213,7 +9213,7 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="28" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B16" s="28">
         <v>2019</v>
@@ -9227,7 +9227,7 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="28" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B17" s="28">
         <v>2019</v>
@@ -9255,7 +9255,7 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="28" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B19" s="28">
         <v>2019</v>
@@ -9269,7 +9269,7 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="28" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B20" s="28">
         <v>2019</v>
@@ -9320,21 +9320,21 @@
         <v>5</v>
       </c>
       <c r="B1" t="s">
+        <v>377</v>
+      </c>
+      <c r="C1" t="s">
         <v>378</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>379</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>380</v>
-      </c>
-      <c r="E1" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B2">
         <v>55</v>
@@ -9351,7 +9351,7 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B3">
         <v>55</v>
@@ -9368,7 +9368,7 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B4">
         <v>44</v>
@@ -9385,7 +9385,7 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -9402,7 +9402,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -9419,7 +9419,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B7">
         <v>9</v>
@@ -9436,7 +9436,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B8">
         <v>42</v>
@@ -9453,7 +9453,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B9">
         <v>44</v>
@@ -9491,18 +9491,18 @@
         <v>22</v>
       </c>
       <c r="B1" t="s">
+        <v>386</v>
+      </c>
+      <c r="C1" t="s">
         <v>387</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>388</v>
-      </c>
-      <c r="D1" t="s">
-        <v>389</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B2" s="29">
         <v>93288</v>
@@ -9516,7 +9516,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B3" s="29">
         <v>1077</v>
@@ -9530,7 +9530,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B4" s="29">
         <v>40190</v>
@@ -9544,7 +9544,7 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B5" s="29">
         <v>7721</v>
@@ -9558,7 +9558,7 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B6" s="29">
         <v>8020</v>
@@ -9572,7 +9572,7 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B7" s="29">
         <v>4263</v>
@@ -9586,7 +9586,7 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B8" s="29">
         <v>6774</v>
@@ -9600,7 +9600,7 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B9" s="29">
         <v>14662</v>
@@ -9614,7 +9614,7 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B10" s="29">
         <v>5459</v>
@@ -9628,7 +9628,7 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B11" s="29">
         <v>15407</v>
@@ -9662,15 +9662,15 @@
         <v>22</v>
       </c>
       <c r="B1" t="s">
+        <v>399</v>
+      </c>
+      <c r="C1" t="s">
         <v>400</v>
-      </c>
-      <c r="C1" t="s">
-        <v>401</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B2" s="30">
         <v>0.22</v>
@@ -9681,7 +9681,7 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B3" s="30">
         <v>0.11</v>
@@ -9692,7 +9692,7 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B4" s="30">
         <v>0.53</v>
@@ -9703,7 +9703,7 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B5" s="30">
         <v>0.19</v>
@@ -9714,7 +9714,7 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B6" s="30">
         <v>0.21</v>
@@ -9725,7 +9725,7 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B7" s="30">
         <v>0.16</v>
@@ -9736,7 +9736,7 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B8" s="30">
         <v>0.12</v>
@@ -9747,7 +9747,7 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B9" s="30">
         <v>0.83</v>
@@ -9758,7 +9758,7 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B10" s="30">
         <v>0.72</v>
@@ -9769,7 +9769,7 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B11" s="30">
         <v>0.54</v>
@@ -9817,7 +9817,7 @@
         <v>12</v>
       </c>
       <c r="I1" s="26" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -10197,13 +10197,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="26" t="s">
+        <v>402</v>
+      </c>
+      <c r="C1" s="26" t="s">
         <v>403</v>
       </c>
-      <c r="C1" s="26" t="s">
+      <c r="D1" s="26" t="s">
         <v>404</v>
-      </c>
-      <c r="D1" s="26" t="s">
-        <v>405</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -10471,24 +10471,24 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="25" t="s">
+        <v>405</v>
+      </c>
+      <c r="B1" s="26" t="s">
         <v>406</v>
       </c>
-      <c r="B1" s="26" t="s">
+      <c r="C1" s="26" t="s">
         <v>407</v>
       </c>
-      <c r="C1" s="26" t="s">
+      <c r="D1" s="26" t="s">
         <v>408</v>
       </c>
-      <c r="D1" s="26" t="s">
+      <c r="E1" s="26" t="s">
         <v>409</v>
-      </c>
-      <c r="E1" s="26" t="s">
-        <v>410</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="27" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B2" s="27">
         <v>115</v>
@@ -10505,7 +10505,7 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="27" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B3" s="27">
         <v>120</v>
@@ -10522,7 +10522,7 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="27" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B4" s="27">
         <v>140</v>
@@ -10556,26 +10556,26 @@
   <sheetData>
     <row r="1" spans="1:2" ht="15">
       <c r="A1" s="25" t="s">
+        <v>413</v>
+      </c>
+      <c r="B1" s="26" t="s">
         <v>414</v>
-      </c>
-      <c r="B1" s="26" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="15">
       <c r="A2" s="27" t="s">
+        <v>415</v>
+      </c>
+      <c r="B2" s="27" t="s">
         <v>416</v>
-      </c>
-      <c r="B2" s="27" t="s">
-        <v>417</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="15">
       <c r="A3" s="27" t="s">
+        <v>417</v>
+      </c>
+      <c r="B3" s="27" t="s">
         <v>418</v>
-      </c>
-      <c r="B3" s="27" t="s">
-        <v>419</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="15">
@@ -10583,23 +10583,23 @@
         <v>357</v>
       </c>
       <c r="B4" s="27" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="15">
       <c r="A5" s="27" t="s">
+        <v>420</v>
+      </c>
+      <c r="B5" s="27" t="s">
         <v>421</v>
-      </c>
-      <c r="B5" s="27" t="s">
-        <v>422</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="27" t="s">
+        <v>422</v>
+      </c>
+      <c r="B6" s="27" t="s">
         <v>423</v>
-      </c>
-      <c r="B6" s="27" t="s">
-        <v>424</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="15"/>
@@ -10628,10 +10628,10 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="25" t="s">
+        <v>424</v>
+      </c>
+      <c r="B1" s="26" t="s">
         <v>425</v>
-      </c>
-      <c r="B1" s="26" t="s">
-        <v>426</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -10644,7 +10644,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="27" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B3" s="27">
         <v>44</v>
@@ -10652,7 +10652,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="27" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B4" s="27">
         <v>33</v>
@@ -10660,7 +10660,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="27" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B5" s="27">
         <v>11</v>
@@ -10668,7 +10668,7 @@
     </row>
     <row r="12" spans="1:10">
       <c r="J12" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
   </sheetData>
@@ -10691,7 +10691,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="15">
       <c r="A1" s="25" t="s">
-        <v>358</v>
+        <v>428</v>
       </c>
       <c r="B1" s="26" t="s">
         <v>14</v>
@@ -10750,7 +10750,7 @@
         <v>432</v>
       </c>
       <c r="B1" s="26" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -11432,7 +11432,7 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>461</v>
@@ -11508,7 +11508,7 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
@@ -11542,7 +11542,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="14.25">
       <c r="A1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B1" t="s">
         <v>480</v>
@@ -11789,7 +11789,7 @@
     </row>
     <row r="2" spans="1:8" ht="14.25">
       <c r="A2" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B2" t="s">
         <v>485</v>
@@ -11994,7 +11994,7 @@
         <v>489</v>
       </c>
       <c r="B1" s="28" t="s">
-        <v>358</v>
+        <v>428</v>
       </c>
       <c r="C1" s="28" t="s">
         <v>490</v>
@@ -19066,24 +19066,24 @@
         <v>22</v>
       </c>
       <c r="B1" t="s">
+        <v>386</v>
+      </c>
+      <c r="C1" t="s">
         <v>387</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>388</v>
       </c>
-      <c r="D1" t="s">
-        <v>389</v>
-      </c>
       <c r="E1" t="s">
+        <v>399</v>
+      </c>
+      <c r="F1" t="s">
         <v>400</v>
-      </c>
-      <c r="F1" t="s">
-        <v>401</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="14.25">
       <c r="A2" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B2" s="29">
         <v>93288</v>
@@ -19103,7 +19103,7 @@
     </row>
     <row r="3" spans="1:6" ht="14.25">
       <c r="A3" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B3" s="29">
         <v>1077</v>
@@ -19123,7 +19123,7 @@
     </row>
     <row r="4" spans="1:6" ht="14.25">
       <c r="A4" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B4" s="29">
         <v>40190</v>
@@ -19143,7 +19143,7 @@
     </row>
     <row r="5" spans="1:6" ht="14.25">
       <c r="A5" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B5" s="29">
         <v>7721</v>
@@ -19163,7 +19163,7 @@
     </row>
     <row r="6" spans="1:6" ht="14.25">
       <c r="A6" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B6" s="29">
         <v>8020</v>
@@ -19183,7 +19183,7 @@
     </row>
     <row r="7" spans="1:6" ht="14.25">
       <c r="A7" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B7" s="29">
         <v>4263</v>
@@ -19203,7 +19203,7 @@
     </row>
     <row r="8" spans="1:6" ht="14.25">
       <c r="A8" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B8" s="29">
         <v>6774</v>
@@ -19223,7 +19223,7 @@
     </row>
     <row r="9" spans="1:6" ht="14.25">
       <c r="A9" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B9" s="29">
         <v>14662</v>
@@ -19243,7 +19243,7 @@
     </row>
     <row r="10" spans="1:6" ht="14.25">
       <c r="A10" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B10" s="29">
         <v>5459</v>
@@ -19263,7 +19263,7 @@
     </row>
     <row r="11" spans="1:6" ht="14.25">
       <c r="A11" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B11" s="29">
         <v>15407</v>
@@ -19297,26 +19297,26 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="25" t="s">
+        <v>413</v>
+      </c>
+      <c r="B1" s="26" t="s">
         <v>414</v>
-      </c>
-      <c r="B1" s="26" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="27" t="s">
+        <v>415</v>
+      </c>
+      <c r="B2" s="27" t="s">
         <v>416</v>
-      </c>
-      <c r="B2" s="27" t="s">
-        <v>417</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="27" t="s">
+        <v>417</v>
+      </c>
+      <c r="B3" s="27" t="s">
         <v>418</v>
-      </c>
-      <c r="B3" s="27" t="s">
-        <v>419</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -19324,31 +19324,31 @@
         <v>357</v>
       </c>
       <c r="B4" s="27" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="27" t="s">
+        <v>420</v>
+      </c>
+      <c r="B5" s="27" t="s">
         <v>421</v>
-      </c>
-      <c r="B5" s="27" t="s">
-        <v>422</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="27" t="s">
+        <v>422</v>
+      </c>
+      <c r="B6" s="27" t="s">
         <v>423</v>
-      </c>
-      <c r="B6" s="27" t="s">
-        <v>424</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="25" t="s">
+        <v>424</v>
+      </c>
+      <c r="B7" s="26" t="s">
         <v>425</v>
-      </c>
-      <c r="B7" s="26" t="s">
-        <v>426</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -19361,7 +19361,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="27" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B9" s="27">
         <v>44</v>
@@ -19369,7 +19369,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="27" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B10" s="27">
         <v>33</v>
@@ -19377,7 +19377,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="27" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B11" s="27">
         <v>11</v>
@@ -19395,7 +19395,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="14.25">
       <c r="A1" s="25" t="s">
-        <v>358</v>
+        <v>428</v>
       </c>
       <c r="B1" s="26" t="s">
         <v>494</v>
@@ -19404,7 +19404,7 @@
         <v>495</v>
       </c>
       <c r="D1" s="26" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="14.25">
@@ -19440,7 +19440,7 @@
         <v>432</v>
       </c>
       <c r="B4" s="26" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -24815,6 +24815,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="c8670835-afc4-4376-8ae0-1ffed5b27e6b" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b0bf4113-6f4a-4f3e-b5bb-503c4d9102e3">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010098970033F315F542A2D9640B7CC02236" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="94449e8ff35cec47b43afd2e381d9e90">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b0bf4113-6f4a-4f3e-b5bb-503c4d9102e3" xmlns:ns3="c8670835-afc4-4376-8ae0-1ffed5b27e6b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f7f21ad7dc1dad656b5a5a7699096a32" ns2:_="" ns3:_="">
     <xsd:import namespace="b0bf4113-6f4a-4f3e-b5bb-503c4d9102e3"/>
@@ -25055,34 +25075,14 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="c8670835-afc4-4376-8ae0-1ffed5b27e6b" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b0bf4113-6f4a-4f3e-b5bb-503c4d9102e3">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA2588C5-0196-4360-8A98-A8906953FDD2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A7E9460-F128-4419-BA1C-5413CC6C046F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A7E9460-F128-4419-BA1C-5413CC6C046F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF42F510-D400-4F69-838A-213F2CB9A7EF}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF42F510-D400-4F69-838A-213F2CB9A7EF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA2588C5-0196-4360-8A98-A8906953FDD2}"/>
 </file>
--- a/02_Inputs/Data/Charts/Module 2 - Datasets for Charts.xlsx
+++ b/02_Inputs/Data/Charts/Module 2 - Datasets for Charts.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29016"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://undp.sharepoint.com/sites/SEHCoreTeam/Shared Documents/General/04. Sustainable Energy Academy/SEA Charts and Infographics/SEA - Charts/Datasets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="947" documentId="11_C37B7BF874E036F1B873F16424B654186DDE5F8D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{23D66403-AD8F-445C-9F09-88C9908CC680}"/>
+  <xr:revisionPtr revIDLastSave="956" documentId="11_C37B7BF874E036F1B873F16424B654186DDE5F8D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{239BACEA-B8DC-443C-BBB6-8E359F00E6A6}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="16" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="25" activeTab="25" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="M2_C2_47_1" sheetId="16" r:id="rId1"/>
@@ -1384,10 +1384,10 @@
     <t>Group</t>
   </si>
   <si>
-    <t>National electrification rate [%]</t>
-  </si>
-  <si>
-    <t>Rural electrification rate [%]</t>
+    <t>National electrification rate</t>
+  </si>
+  <si>
+    <t>Rural electrification rate</t>
   </si>
   <si>
     <t>Low-Income Economies (USD 1 135 or less)</t>
@@ -10777,19 +10777,19 @@
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBBA9ACB-4A6F-4733-A934-7EEB633D3300}">
   <sheetPr>
-    <tabColor rgb="FFFFFF00"/>
+    <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A1:E36"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="38.5703125" customWidth="1"/>
+    <col min="1" max="1" width="89.28515625" customWidth="1"/>
     <col min="2" max="2" width="13.7109375" customWidth="1"/>
     <col min="3" max="3" width="30.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20.7109375" customWidth="1"/>
     <col min="5" max="5" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="28.5">
+    <row r="1" spans="1:5" ht="29.25">
       <c r="A1" s="7" t="s">
         <v>435</v>
       </c>
@@ -22663,6 +22663,9 @@
   </sheetPr>
   <dimension ref="A1:C195"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="15.85546875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
@@ -24815,15 +24818,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="c8670835-afc4-4376-8ae0-1ffed5b27e6b" xsi:nil="true"/>
@@ -24834,7 +24828,7 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010098970033F315F542A2D9640B7CC02236" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="94449e8ff35cec47b43afd2e381d9e90">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b0bf4113-6f4a-4f3e-b5bb-503c4d9102e3" xmlns:ns3="c8670835-afc4-4376-8ae0-1ffed5b27e6b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f7f21ad7dc1dad656b5a5a7699096a32" ns2:_="" ns3:_="">
     <xsd:import namespace="b0bf4113-6f4a-4f3e-b5bb-503c4d9102e3"/>
@@ -25075,14 +25069,23 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A7E9460-F128-4419-BA1C-5413CC6C046F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF42F510-D400-4F69-838A-213F2CB9A7EF}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF42F510-D400-4F69-838A-213F2CB9A7EF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA2588C5-0196-4360-8A98-A8906953FDD2}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA2588C5-0196-4360-8A98-A8906953FDD2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A7E9460-F128-4419-BA1C-5413CC6C046F}"/>
 </file>
--- a/02_Inputs/Data/Charts/Module 2 - Datasets for Charts.xlsx
+++ b/02_Inputs/Data/Charts/Module 2 - Datasets for Charts.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29016"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29019"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://undp.sharepoint.com/sites/SEHCoreTeam/Shared Documents/General/04. Sustainable Energy Academy/SEA Charts and Infographics/SEA - Charts/Datasets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="956" documentId="11_C37B7BF874E036F1B873F16424B654186DDE5F8D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{239BACEA-B8DC-443C-BBB6-8E359F00E6A6}"/>
+  <xr:revisionPtr revIDLastSave="965" documentId="11_C37B7BF874E036F1B873F16424B654186DDE5F8D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9664357C-0927-43A2-9301-776888609F7F}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="25" activeTab="25" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="25" activeTab="20" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="M2_C2_47_1" sheetId="16" r:id="rId1"/>
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2028" uniqueCount="496">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2023" uniqueCount="497">
   <si>
     <t>Year</t>
   </si>
@@ -1279,28 +1279,28 @@
     <t>Unspecified countries</t>
   </si>
   <si>
-    <t>LDCs (USD bn)</t>
-  </si>
-  <si>
-    <t>LLDCs (USD bn)</t>
-  </si>
-  <si>
-    <t>SIDS (USD bn)</t>
+    <t>LDCs</t>
+  </si>
+  <si>
+    <t>LLDCs</t>
+  </si>
+  <si>
+    <t>SIDS</t>
   </si>
   <si>
     <t>Scenario</t>
   </si>
   <si>
-    <t>Grid (USD bn)</t>
-  </si>
-  <si>
-    <t>Mini-grid (USD bn)</t>
-  </si>
-  <si>
-    <t>Stand-alone (USD bn)</t>
-  </si>
-  <si>
-    <t>Total (USD bn)</t>
+    <t>Grid</t>
+  </si>
+  <si>
+    <t>Mini-grid</t>
+  </si>
+  <si>
+    <t>Stand-alone</t>
+  </si>
+  <si>
+    <t>Total</t>
   </si>
   <si>
     <t>Low Demand</t>
@@ -1315,34 +1315,19 @@
     <t>Category</t>
   </si>
   <si>
-    <t>Population</t>
+    <t>Population (billions)</t>
   </si>
   <si>
     <t>Natural gas</t>
   </si>
   <si>
-    <t>1.68 billion</t>
-  </si>
-  <si>
     <t>LPG</t>
   </si>
   <si>
-    <t>1.48 billion</t>
-  </si>
-  <si>
-    <t>890 million</t>
-  </si>
-  <si>
     <t>Biogas &amp; ethanol</t>
   </si>
   <si>
-    <t>232 million</t>
-  </si>
-  <si>
     <t>People without access</t>
-  </si>
-  <si>
-    <t>2 billion</t>
   </si>
   <si>
     <t>Solution</t>
@@ -1515,6 +1500,9 @@
     <t xml:space="preserve">Sudan </t>
   </si>
   <si>
+    <t>Population</t>
+  </si>
+  <si>
     <t>Unit</t>
   </si>
   <si>
@@ -1554,13 +1542,28 @@
     <t>Proportion of population with primary reliance on fuels and technologies for cooking, by fuel type (%)</t>
   </si>
   <si>
-    <t>Total</t>
+    <t>1.68 billion</t>
+  </si>
+  <si>
+    <t>1.48 billion</t>
+  </si>
+  <si>
+    <t>890 million</t>
+  </si>
+  <si>
+    <t>232 million</t>
+  </si>
+  <si>
+    <t>2 billion</t>
   </si>
   <si>
     <t>Sub-Saharan Africa (USD bn)</t>
   </si>
   <si>
     <t>Rest of World (USD bn)</t>
+  </si>
+  <si>
+    <t>Total (USD bn)</t>
   </si>
 </sst>
 </file>
@@ -10558,7 +10561,7 @@
       <c r="A1" s="25" t="s">
         <v>413</v>
       </c>
-      <c r="B1" s="26" t="s">
+      <c r="B1" t="s">
         <v>414</v>
       </c>
     </row>
@@ -10566,40 +10569,40 @@
       <c r="A2" s="27" t="s">
         <v>415</v>
       </c>
-      <c r="B2" s="27" t="s">
-        <v>416</v>
+      <c r="B2" s="27">
+        <v>1.68</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="15">
       <c r="A3" s="27" t="s">
-        <v>417</v>
-      </c>
-      <c r="B3" s="27" t="s">
-        <v>418</v>
+        <v>416</v>
+      </c>
+      <c r="B3" s="27">
+        <v>1.48</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="15">
       <c r="A4" s="27" t="s">
         <v>357</v>
       </c>
-      <c r="B4" s="27" t="s">
-        <v>419</v>
+      <c r="B4" s="27">
+        <v>0.89</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="15">
       <c r="A5" s="27" t="s">
-        <v>420</v>
-      </c>
-      <c r="B5" s="27" t="s">
-        <v>421</v>
+        <v>417</v>
+      </c>
+      <c r="B5" s="27">
+        <v>0.23</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="27" t="s">
-        <v>422</v>
-      </c>
-      <c r="B6" s="27" t="s">
-        <v>423</v>
+        <v>418</v>
+      </c>
+      <c r="B6" s="27">
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="15"/>
@@ -10628,10 +10631,10 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="25" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="B1" s="26" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -10644,7 +10647,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="27" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B3" s="27">
         <v>44</v>
@@ -10652,7 +10655,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="27" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="B4" s="27">
         <v>33</v>
@@ -10660,7 +10663,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="27" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="B5" s="27">
         <v>11</v>
@@ -10668,7 +10671,7 @@
     </row>
     <row r="12" spans="1:10">
       <c r="J12" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
     </row>
   </sheetData>
@@ -10691,18 +10694,18 @@
   <sheetData>
     <row r="1" spans="1:3" ht="15">
       <c r="A1" s="25" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="B1" s="26" t="s">
         <v>14</v>
       </c>
       <c r="C1" s="26" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="15">
       <c r="A2" s="27" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="B2" s="27">
         <v>0.2</v>
@@ -10713,7 +10716,7 @@
     </row>
     <row r="3" spans="1:3" ht="15">
       <c r="A3" s="27" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="B3" s="27">
         <v>4</v>
@@ -10747,15 +10750,15 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="25" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="B1" s="26" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="27" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="B2" s="27">
         <v>21</v>
@@ -10763,7 +10766,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="27" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="B3" s="27">
         <v>79</v>
@@ -10791,27 +10794,27 @@
   <sheetData>
     <row r="1" spans="1:5" ht="29.25">
       <c r="A1" s="7" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="C1" s="7" t="s">
         <v>22</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="9" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="C2" s="10" t="s">
         <v>150</v>
@@ -10825,10 +10828,10 @@
     </row>
     <row r="3" spans="1:5" ht="28.5">
       <c r="A3" s="20" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="B3" s="18" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="C3" s="11" t="s">
         <v>73</v>
@@ -10842,10 +10845,10 @@
     </row>
     <row r="4" spans="1:5" ht="28.5">
       <c r="A4" s="20" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="C4" s="11" t="s">
         <v>89</v>
@@ -10859,13 +10862,13 @@
     </row>
     <row r="5" spans="1:5" ht="28.5">
       <c r="A5" s="20" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="D5" s="19">
         <v>78.491620111731805</v>
@@ -10876,13 +10879,13 @@
     </row>
     <row r="6" spans="1:5" ht="28.5">
       <c r="A6" s="20" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="D6" s="19">
         <v>47.3580074487895</v>
@@ -10893,13 +10896,13 @@
     </row>
     <row r="7" spans="1:5" ht="28.5">
       <c r="A7" s="20" t="s">
+        <v>436</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>440</v>
+      </c>
+      <c r="C7" s="11" t="s">
         <v>441</v>
-      </c>
-      <c r="B7" s="18" t="s">
-        <v>445</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>446</v>
       </c>
       <c r="D7" s="19">
         <v>92.652079453755405</v>
@@ -10910,13 +10913,13 @@
     </row>
     <row r="8" spans="1:5" ht="28.5">
       <c r="A8" s="20" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="D8" s="19">
         <v>83.244103041589</v>
@@ -10927,10 +10930,10 @@
     </row>
     <row r="9" spans="1:5" ht="28.5">
       <c r="A9" s="20" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>249</v>
@@ -10944,10 +10947,10 @@
     </row>
     <row r="10" spans="1:5" ht="28.5">
       <c r="A10" s="20" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>272</v>
@@ -10961,10 +10964,10 @@
     </row>
     <row r="11" spans="1:5" ht="28.5">
       <c r="A11" s="20" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>288</v>
@@ -10978,10 +10981,10 @@
     </row>
     <row r="12" spans="1:5" ht="28.5">
       <c r="A12" s="20" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="C12" s="11" t="s">
         <v>313</v>
@@ -10995,10 +10998,10 @@
     </row>
     <row r="13" spans="1:5" ht="28.5">
       <c r="A13" s="20" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="C13" s="11" t="s">
         <v>338</v>
@@ -11012,10 +11015,10 @@
     </row>
     <row r="14" spans="1:5" ht="42.75">
       <c r="A14" s="21" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="B14" s="22" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="C14" s="12" t="s">
         <v>201</v>
@@ -11029,10 +11032,10 @@
     </row>
     <row r="15" spans="1:5" ht="42.75">
       <c r="A15" s="21" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="B15" s="22" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="C15" s="12" t="s">
         <v>210</v>
@@ -11046,10 +11049,10 @@
     </row>
     <row r="16" spans="1:5" ht="42.75">
       <c r="A16" s="21" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="B16" s="22" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="C16" s="12" t="s">
         <v>52</v>
@@ -11063,10 +11066,10 @@
     </row>
     <row r="17" spans="1:5" ht="42.75">
       <c r="A17" s="21" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="B17" s="22" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="C17" s="12" t="s">
         <v>100</v>
@@ -11080,10 +11083,10 @@
     </row>
     <row r="18" spans="1:5" ht="42.75">
       <c r="A18" s="21" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="B18" s="22" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="C18" s="12" t="s">
         <v>111</v>
@@ -11097,13 +11100,13 @@
     </row>
     <row r="19" spans="1:5" ht="42.75">
       <c r="A19" s="21" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="B19" s="22" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="D19" s="16">
         <v>98.180477963997504</v>
@@ -11114,13 +11117,13 @@
     </row>
     <row r="20" spans="1:5" ht="42.75">
       <c r="A20" s="21" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="B20" s="22" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="D20" s="16">
         <v>93.7189633767846</v>
@@ -11131,13 +11134,13 @@
     </row>
     <row r="21" spans="1:5" ht="42.75">
       <c r="A21" s="21" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="B21" s="22" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="D21" s="16">
         <v>100</v>
@@ -11148,13 +11151,13 @@
     </row>
     <row r="22" spans="1:5" ht="42.75">
       <c r="A22" s="21" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="B22" s="22" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="D22" s="16">
         <v>100</v>
@@ -11165,10 +11168,10 @@
     </row>
     <row r="23" spans="1:5" ht="42.75">
       <c r="A23" s="21" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="B23" s="22" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="C23" s="13" t="s">
         <v>268</v>
@@ -11182,10 +11185,10 @@
     </row>
     <row r="24" spans="1:5" ht="42.75">
       <c r="A24" s="21" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="B24" s="22" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="C24" s="12" t="s">
         <v>270</v>
@@ -11199,10 +11202,10 @@
     </row>
     <row r="25" spans="1:5" ht="42.75">
       <c r="A25" s="21" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="B25" s="22" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="C25" s="12" t="s">
         <v>301</v>
@@ -11216,10 +11219,10 @@
     </row>
     <row r="26" spans="1:5" ht="42.75">
       <c r="A26" s="21" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="B26" s="22" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="C26" s="12" t="s">
         <v>130</v>
@@ -11233,10 +11236,10 @@
     </row>
     <row r="27" spans="1:5" ht="42.75">
       <c r="A27" s="21" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="B27" s="22" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="C27" s="12" t="s">
         <v>206</v>
@@ -11250,13 +11253,13 @@
     </row>
     <row r="28" spans="1:5" ht="42.75">
       <c r="A28" s="21" t="s">
+        <v>443</v>
+      </c>
+      <c r="B28" s="22" t="s">
+        <v>440</v>
+      </c>
+      <c r="C28" s="13" t="s">
         <v>448</v>
-      </c>
-      <c r="B28" s="22" t="s">
-        <v>445</v>
-      </c>
-      <c r="C28" s="13" t="s">
-        <v>453</v>
       </c>
       <c r="D28" s="16">
         <v>100</v>
@@ -11267,13 +11270,13 @@
     </row>
     <row r="29" spans="1:5" ht="42.75">
       <c r="A29" s="21" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="B29" s="22" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="D29" s="16">
         <v>100</v>
@@ -11284,10 +11287,10 @@
     </row>
     <row r="30" spans="1:5" ht="42.75">
       <c r="A30" s="21" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="B30" s="22" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="C30" s="13" t="s">
         <v>324</v>
@@ -11301,10 +11304,10 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="20" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="C31" s="14" t="s">
         <v>282</v>
@@ -11318,13 +11321,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="20" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="C32" s="14" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="D32" s="19">
         <v>99.926288019863406</v>
@@ -11335,10 +11338,10 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="20" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="B33" s="23" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="C33" s="15" t="s">
         <v>152</v>
@@ -11352,10 +11355,10 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="20" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="C34" s="14" t="s">
         <v>228</v>
@@ -11369,10 +11372,10 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="22" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="B35" s="22" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="C35" s="12" t="s">
         <v>93</v>
@@ -11386,10 +11389,10 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="22" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="B36" s="22" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="C36" s="12" t="s">
         <v>239</v>
@@ -11421,13 +11424,13 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="2" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -11435,73 +11438,73 @@
         <v>397</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="1" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="1" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="C5" s="1"/>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="1" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="C6" s="1"/>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="1" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="C7" s="1"/>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="1" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="C8" s="1"/>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="1" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -11515,14 +11518,14 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="1" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="1" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -11542,10 +11545,10 @@
   <sheetData>
     <row r="1" spans="1:6" ht="14.25">
       <c r="A1" t="s">
-        <v>414</v>
+        <v>475</v>
       </c>
       <c r="B1" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="C1">
         <v>2010</v>
@@ -11565,7 +11568,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="C2">
         <v>5.8</v>
@@ -11585,7 +11588,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="C3">
         <v>1.1000000000000001</v>
@@ -11602,10 +11605,10 @@
     </row>
     <row r="4" spans="1:6" ht="14.25">
       <c r="A4" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="B4" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="C4">
         <v>84</v>
@@ -11639,13 +11642,13 @@
   <sheetData>
     <row r="1" spans="1:5" ht="15" customHeight="1">
       <c r="B1" s="32" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="C1" s="32" t="s">
         <v>7</v>
       </c>
       <c r="D1" s="32" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="E1" s="32" t="s">
         <v>7</v>
@@ -11789,10 +11792,10 @@
     </row>
     <row r="2" spans="1:8" ht="14.25">
       <c r="A2" t="s">
-        <v>414</v>
+        <v>475</v>
       </c>
       <c r="B2" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="C2">
         <v>2010</v>
@@ -11818,7 +11821,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="C3">
         <v>3416</v>
@@ -11844,7 +11847,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="C4">
         <v>145</v>
@@ -11867,10 +11870,10 @@
     </row>
     <row r="5" spans="1:8" ht="14.25">
       <c r="A5" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="B5" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="C5">
         <v>0.1</v>
@@ -11887,10 +11890,10 @@
     </row>
     <row r="6" spans="1:8" ht="14.25">
       <c r="A6" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="B6" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="C6">
         <v>96</v>
@@ -11991,16 +11994,16 @@
   <sheetData>
     <row r="1" spans="1:5" ht="14.25">
       <c r="A1" s="28" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="B1" s="28" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="C1" s="28" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="D1" s="28" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="E1" s="28" t="s">
         <v>23</v>
@@ -12008,7 +12011,7 @@
     </row>
     <row r="2" spans="1:5" ht="14.25">
       <c r="A2" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B2" s="28">
         <v>2022</v>
@@ -12025,13 +12028,13 @@
     </row>
     <row r="3" spans="1:5" ht="14.25">
       <c r="A3" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B3" s="28">
         <v>2022</v>
       </c>
       <c r="C3" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D3" s="28" t="s">
         <v>353</v>
@@ -12042,7 +12045,7 @@
     </row>
     <row r="4" spans="1:5" ht="14.25">
       <c r="A4" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B4" s="28">
         <v>2022</v>
@@ -12059,7 +12062,7 @@
     </row>
     <row r="5" spans="1:5" ht="14.25">
       <c r="A5" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B5" s="28">
         <v>2022</v>
@@ -12076,13 +12079,13 @@
     </row>
     <row r="6" spans="1:5" ht="14.25">
       <c r="A6" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B6" s="28">
         <v>2022</v>
       </c>
       <c r="C6" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D6" s="28" t="s">
         <v>352</v>
@@ -12093,7 +12096,7 @@
     </row>
     <row r="7" spans="1:5" ht="14.25">
       <c r="A7" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B7" s="28">
         <v>2022</v>
@@ -12110,7 +12113,7 @@
     </row>
     <row r="8" spans="1:5" ht="14.25">
       <c r="A8" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B8" s="28">
         <v>2022</v>
@@ -12127,13 +12130,13 @@
     </row>
     <row r="9" spans="1:5" ht="14.25">
       <c r="A9" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B9" s="28">
         <v>2022</v>
       </c>
       <c r="C9" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D9" s="28" t="s">
         <v>356</v>
@@ -12144,13 +12147,13 @@
     </row>
     <row r="10" spans="1:5" ht="14.25">
       <c r="A10" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B10" s="28">
         <v>2022</v>
       </c>
       <c r="C10" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D10" s="28" t="s">
         <v>354</v>
@@ -12161,7 +12164,7 @@
     </row>
     <row r="11" spans="1:5" ht="14.25">
       <c r="A11" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B11" s="28">
         <v>2022</v>
@@ -12178,7 +12181,7 @@
     </row>
     <row r="12" spans="1:5" ht="14.25">
       <c r="A12" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B12" s="28">
         <v>2022</v>
@@ -12195,7 +12198,7 @@
     </row>
     <row r="13" spans="1:5" ht="14.25">
       <c r="A13" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B13" s="28">
         <v>2022</v>
@@ -12212,13 +12215,13 @@
     </row>
     <row r="14" spans="1:5" ht="14.25">
       <c r="A14" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B14" s="28">
         <v>2022</v>
       </c>
       <c r="C14" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D14" s="28" t="s">
         <v>355</v>
@@ -12229,7 +12232,7 @@
     </row>
     <row r="15" spans="1:5" ht="14.25">
       <c r="A15" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B15" s="28">
         <v>2022</v>
@@ -12246,7 +12249,7 @@
     </row>
     <row r="16" spans="1:5" ht="14.25">
       <c r="A16" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B16" s="28">
         <v>2022</v>
@@ -12263,7 +12266,7 @@
     </row>
     <row r="17" spans="1:5" ht="14.25">
       <c r="A17" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B17" s="28">
         <v>2022</v>
@@ -12280,13 +12283,13 @@
     </row>
     <row r="18" spans="1:5" ht="14.25">
       <c r="A18" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B18" s="28">
         <v>2022</v>
       </c>
       <c r="C18" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D18" s="28" t="s">
         <v>357</v>
@@ -12297,7 +12300,7 @@
     </row>
     <row r="19" spans="1:5" ht="14.25">
       <c r="A19" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B19" s="28">
         <v>2022</v>
@@ -12314,7 +12317,7 @@
     </row>
     <row r="20" spans="1:5" ht="14.25">
       <c r="A20" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B20" s="28">
         <v>2021</v>
@@ -12331,13 +12334,13 @@
     </row>
     <row r="21" spans="1:5" ht="14.25">
       <c r="A21" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B21" s="28">
         <v>2021</v>
       </c>
       <c r="C21" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D21" s="28" t="s">
         <v>353</v>
@@ -12348,7 +12351,7 @@
     </row>
     <row r="22" spans="1:5" ht="14.25">
       <c r="A22" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B22" s="28">
         <v>2021</v>
@@ -12365,13 +12368,13 @@
     </row>
     <row r="23" spans="1:5" ht="14.25">
       <c r="A23" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B23" s="28">
         <v>2021</v>
       </c>
       <c r="C23" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D23" s="28" t="s">
         <v>352</v>
@@ -12382,7 +12385,7 @@
     </row>
     <row r="24" spans="1:5" ht="14.25">
       <c r="A24" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B24" s="28">
         <v>2021</v>
@@ -12399,7 +12402,7 @@
     </row>
     <row r="25" spans="1:5" ht="14.25">
       <c r="A25" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B25" s="28">
         <v>2021</v>
@@ -12416,7 +12419,7 @@
     </row>
     <row r="26" spans="1:5" ht="14.25">
       <c r="A26" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B26" s="28">
         <v>2021</v>
@@ -12433,13 +12436,13 @@
     </row>
     <row r="27" spans="1:5" ht="14.25">
       <c r="A27" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B27" s="28">
         <v>2021</v>
       </c>
       <c r="C27" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D27" s="28" t="s">
         <v>356</v>
@@ -12450,13 +12453,13 @@
     </row>
     <row r="28" spans="1:5" ht="14.25">
       <c r="A28" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B28" s="28">
         <v>2021</v>
       </c>
       <c r="C28" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D28" s="28" t="s">
         <v>354</v>
@@ -12467,7 +12470,7 @@
     </row>
     <row r="29" spans="1:5" ht="14.25">
       <c r="A29" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B29" s="28">
         <v>2021</v>
@@ -12484,7 +12487,7 @@
     </row>
     <row r="30" spans="1:5" ht="14.25">
       <c r="A30" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B30" s="28">
         <v>2021</v>
@@ -12501,7 +12504,7 @@
     </row>
     <row r="31" spans="1:5" ht="14.25">
       <c r="A31" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B31" s="28">
         <v>2021</v>
@@ -12518,13 +12521,13 @@
     </row>
     <row r="32" spans="1:5" ht="14.25">
       <c r="A32" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B32" s="28">
         <v>2021</v>
       </c>
       <c r="C32" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D32" s="28" t="s">
         <v>355</v>
@@ -12535,7 +12538,7 @@
     </row>
     <row r="33" spans="1:5" ht="14.25">
       <c r="A33" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B33" s="28">
         <v>2021</v>
@@ -12552,7 +12555,7 @@
     </row>
     <row r="34" spans="1:5" ht="14.25">
       <c r="A34" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B34" s="28">
         <v>2021</v>
@@ -12569,7 +12572,7 @@
     </row>
     <row r="35" spans="1:5" ht="14.25">
       <c r="A35" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B35" s="28">
         <v>2021</v>
@@ -12586,13 +12589,13 @@
     </row>
     <row r="36" spans="1:5" ht="14.25">
       <c r="A36" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B36" s="28">
         <v>2021</v>
       </c>
       <c r="C36" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D36" s="28" t="s">
         <v>357</v>
@@ -12603,7 +12606,7 @@
     </row>
     <row r="37" spans="1:5" ht="14.25">
       <c r="A37" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B37" s="28">
         <v>2021</v>
@@ -12620,7 +12623,7 @@
     </row>
     <row r="38" spans="1:5" ht="14.25">
       <c r="A38" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B38" s="28">
         <v>2020</v>
@@ -12637,13 +12640,13 @@
     </row>
     <row r="39" spans="1:5" ht="14.25">
       <c r="A39" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B39" s="28">
         <v>2020</v>
       </c>
       <c r="C39" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D39" s="28" t="s">
         <v>352</v>
@@ -12654,7 +12657,7 @@
     </row>
     <row r="40" spans="1:5" ht="14.25">
       <c r="A40" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B40" s="28">
         <v>2020</v>
@@ -12671,13 +12674,13 @@
     </row>
     <row r="41" spans="1:5" ht="14.25">
       <c r="A41" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B41" s="28">
         <v>2020</v>
       </c>
       <c r="C41" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D41" s="28" t="s">
         <v>353</v>
@@ -12688,7 +12691,7 @@
     </row>
     <row r="42" spans="1:5" ht="14.25">
       <c r="A42" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B42" s="28">
         <v>2020</v>
@@ -12705,7 +12708,7 @@
     </row>
     <row r="43" spans="1:5" ht="14.25">
       <c r="A43" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B43" s="28">
         <v>2020</v>
@@ -12722,7 +12725,7 @@
     </row>
     <row r="44" spans="1:5" ht="14.25">
       <c r="A44" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B44" s="28">
         <v>2020</v>
@@ -12739,13 +12742,13 @@
     </row>
     <row r="45" spans="1:5" ht="14.25">
       <c r="A45" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B45" s="28">
         <v>2020</v>
       </c>
       <c r="C45" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D45" s="28" t="s">
         <v>356</v>
@@ -12756,13 +12759,13 @@
     </row>
     <row r="46" spans="1:5" ht="14.25">
       <c r="A46" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B46" s="28">
         <v>2020</v>
       </c>
       <c r="C46" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D46" s="28" t="s">
         <v>354</v>
@@ -12773,7 +12776,7 @@
     </row>
     <row r="47" spans="1:5" ht="14.25">
       <c r="A47" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B47" s="28">
         <v>2020</v>
@@ -12790,7 +12793,7 @@
     </row>
     <row r="48" spans="1:5" ht="14.25">
       <c r="A48" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B48" s="28">
         <v>2020</v>
@@ -12807,7 +12810,7 @@
     </row>
     <row r="49" spans="1:5" ht="14.25">
       <c r="A49" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B49" s="28">
         <v>2020</v>
@@ -12824,13 +12827,13 @@
     </row>
     <row r="50" spans="1:5" ht="14.25">
       <c r="A50" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B50" s="28">
         <v>2020</v>
       </c>
       <c r="C50" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D50" s="28" t="s">
         <v>355</v>
@@ -12841,7 +12844,7 @@
     </row>
     <row r="51" spans="1:5" ht="14.25">
       <c r="A51" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B51" s="28">
         <v>2020</v>
@@ -12858,7 +12861,7 @@
     </row>
     <row r="52" spans="1:5" ht="14.25">
       <c r="A52" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B52" s="28">
         <v>2020</v>
@@ -12875,13 +12878,13 @@
     </row>
     <row r="53" spans="1:5" ht="14.25">
       <c r="A53" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B53" s="28">
         <v>2020</v>
       </c>
       <c r="C53" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D53" s="28" t="s">
         <v>357</v>
@@ -12892,7 +12895,7 @@
     </row>
     <row r="54" spans="1:5" ht="14.25">
       <c r="A54" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B54" s="28">
         <v>2020</v>
@@ -12909,7 +12912,7 @@
     </row>
     <row r="55" spans="1:5" ht="14.25">
       <c r="A55" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B55" s="28">
         <v>2020</v>
@@ -12926,7 +12929,7 @@
     </row>
     <row r="56" spans="1:5" ht="14.25">
       <c r="A56" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B56" s="28">
         <v>2019</v>
@@ -12943,13 +12946,13 @@
     </row>
     <row r="57" spans="1:5" ht="14.25">
       <c r="A57" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B57" s="28">
         <v>2019</v>
       </c>
       <c r="C57" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D57" s="28" t="s">
         <v>352</v>
@@ -12960,7 +12963,7 @@
     </row>
     <row r="58" spans="1:5" ht="14.25">
       <c r="A58" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B58" s="28">
         <v>2019</v>
@@ -12977,13 +12980,13 @@
     </row>
     <row r="59" spans="1:5" ht="14.25">
       <c r="A59" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B59" s="28">
         <v>2019</v>
       </c>
       <c r="C59" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D59" s="28" t="s">
         <v>353</v>
@@ -12994,7 +12997,7 @@
     </row>
     <row r="60" spans="1:5" ht="14.25">
       <c r="A60" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B60" s="28">
         <v>2019</v>
@@ -13011,7 +13014,7 @@
     </row>
     <row r="61" spans="1:5" ht="14.25">
       <c r="A61" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B61" s="28">
         <v>2019</v>
@@ -13028,7 +13031,7 @@
     </row>
     <row r="62" spans="1:5" ht="14.25">
       <c r="A62" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B62" s="28">
         <v>2019</v>
@@ -13045,7 +13048,7 @@
     </row>
     <row r="63" spans="1:5" ht="14.25">
       <c r="A63" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B63" s="28">
         <v>2019</v>
@@ -13062,13 +13065,13 @@
     </row>
     <row r="64" spans="1:5" ht="14.25">
       <c r="A64" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B64" s="28">
         <v>2019</v>
       </c>
       <c r="C64" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D64" s="28" t="s">
         <v>354</v>
@@ -13079,13 +13082,13 @@
     </row>
     <row r="65" spans="1:5" ht="14.25">
       <c r="A65" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B65" s="28">
         <v>2019</v>
       </c>
       <c r="C65" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D65" s="28" t="s">
         <v>356</v>
@@ -13096,7 +13099,7 @@
     </row>
     <row r="66" spans="1:5" ht="14.25">
       <c r="A66" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B66" s="28">
         <v>2019</v>
@@ -13113,7 +13116,7 @@
     </row>
     <row r="67" spans="1:5" ht="14.25">
       <c r="A67" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B67" s="28">
         <v>2019</v>
@@ -13130,7 +13133,7 @@
     </row>
     <row r="68" spans="1:5" ht="14.25">
       <c r="A68" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B68" s="28">
         <v>2019</v>
@@ -13147,13 +13150,13 @@
     </row>
     <row r="69" spans="1:5" ht="14.25">
       <c r="A69" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B69" s="28">
         <v>2019</v>
       </c>
       <c r="C69" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D69" s="28" t="s">
         <v>355</v>
@@ -13164,7 +13167,7 @@
     </row>
     <row r="70" spans="1:5" ht="14.25">
       <c r="A70" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B70" s="28">
         <v>2019</v>
@@ -13181,7 +13184,7 @@
     </row>
     <row r="71" spans="1:5" ht="14.25">
       <c r="A71" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B71" s="28">
         <v>2019</v>
@@ -13198,13 +13201,13 @@
     </row>
     <row r="72" spans="1:5" ht="14.25">
       <c r="A72" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B72" s="28">
         <v>2019</v>
       </c>
       <c r="C72" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D72" s="28" t="s">
         <v>357</v>
@@ -13215,7 +13218,7 @@
     </row>
     <row r="73" spans="1:5" ht="14.25">
       <c r="A73" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B73" s="28">
         <v>2019</v>
@@ -13232,7 +13235,7 @@
     </row>
     <row r="74" spans="1:5" ht="14.25">
       <c r="A74" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B74" s="28">
         <v>2018</v>
@@ -13249,7 +13252,7 @@
     </row>
     <row r="75" spans="1:5" ht="14.25">
       <c r="A75" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B75" s="28">
         <v>2018</v>
@@ -13266,13 +13269,13 @@
     </row>
     <row r="76" spans="1:5" ht="14.25">
       <c r="A76" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B76" s="28">
         <v>2018</v>
       </c>
       <c r="C76" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D76" s="28" t="s">
         <v>352</v>
@@ -13283,7 +13286,7 @@
     </row>
     <row r="77" spans="1:5" ht="14.25">
       <c r="A77" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B77" s="28">
         <v>2018</v>
@@ -13300,13 +13303,13 @@
     </row>
     <row r="78" spans="1:5" ht="14.25">
       <c r="A78" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B78" s="28">
         <v>2018</v>
       </c>
       <c r="C78" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D78" s="28" t="s">
         <v>353</v>
@@ -13317,7 +13320,7 @@
     </row>
     <row r="79" spans="1:5" ht="14.25">
       <c r="A79" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B79" s="28">
         <v>2018</v>
@@ -13334,7 +13337,7 @@
     </row>
     <row r="80" spans="1:5" ht="14.25">
       <c r="A80" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B80" s="28">
         <v>2018</v>
@@ -13351,7 +13354,7 @@
     </row>
     <row r="81" spans="1:5" ht="14.25">
       <c r="A81" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B81" s="28">
         <v>2018</v>
@@ -13368,13 +13371,13 @@
     </row>
     <row r="82" spans="1:5" ht="14.25">
       <c r="A82" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B82" s="28">
         <v>2018</v>
       </c>
       <c r="C82" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D82" s="28" t="s">
         <v>354</v>
@@ -13385,13 +13388,13 @@
     </row>
     <row r="83" spans="1:5" ht="14.25">
       <c r="A83" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B83" s="28">
         <v>2018</v>
       </c>
       <c r="C83" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D83" s="28" t="s">
         <v>356</v>
@@ -13402,7 +13405,7 @@
     </row>
     <row r="84" spans="1:5" ht="14.25">
       <c r="A84" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B84" s="28">
         <v>2018</v>
@@ -13419,7 +13422,7 @@
     </row>
     <row r="85" spans="1:5" ht="14.25">
       <c r="A85" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B85" s="28">
         <v>2018</v>
@@ -13436,13 +13439,13 @@
     </row>
     <row r="86" spans="1:5" ht="14.25">
       <c r="A86" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B86" s="28">
         <v>2018</v>
       </c>
       <c r="C86" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D86" s="28" t="s">
         <v>355</v>
@@ -13453,7 +13456,7 @@
     </row>
     <row r="87" spans="1:5" ht="14.25">
       <c r="A87" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B87" s="28">
         <v>2018</v>
@@ -13470,7 +13473,7 @@
     </row>
     <row r="88" spans="1:5" ht="14.25">
       <c r="A88" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B88" s="28">
         <v>2018</v>
@@ -13487,7 +13490,7 @@
     </row>
     <row r="89" spans="1:5" ht="14.25">
       <c r="A89" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B89" s="28">
         <v>2018</v>
@@ -13504,13 +13507,13 @@
     </row>
     <row r="90" spans="1:5" ht="14.25">
       <c r="A90" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B90" s="28">
         <v>2018</v>
       </c>
       <c r="C90" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D90" s="28" t="s">
         <v>357</v>
@@ -13521,7 +13524,7 @@
     </row>
     <row r="91" spans="1:5" ht="14.25">
       <c r="A91" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B91" s="28">
         <v>2018</v>
@@ -13538,7 +13541,7 @@
     </row>
     <row r="92" spans="1:5" ht="14.25">
       <c r="A92" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B92" s="28">
         <v>2017</v>
@@ -13555,13 +13558,13 @@
     </row>
     <row r="93" spans="1:5" ht="14.25">
       <c r="A93" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B93" s="28">
         <v>2017</v>
       </c>
       <c r="C93" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D93" s="28" t="s">
         <v>352</v>
@@ -13572,7 +13575,7 @@
     </row>
     <row r="94" spans="1:5" ht="14.25">
       <c r="A94" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B94" s="28">
         <v>2017</v>
@@ -13589,7 +13592,7 @@
     </row>
     <row r="95" spans="1:5" ht="14.25">
       <c r="A95" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B95" s="28">
         <v>2017</v>
@@ -13606,13 +13609,13 @@
     </row>
     <row r="96" spans="1:5" ht="14.25">
       <c r="A96" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B96" s="28">
         <v>2017</v>
       </c>
       <c r="C96" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D96" s="28" t="s">
         <v>353</v>
@@ -13623,7 +13626,7 @@
     </row>
     <row r="97" spans="1:5" ht="14.25">
       <c r="A97" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B97" s="28">
         <v>2017</v>
@@ -13640,7 +13643,7 @@
     </row>
     <row r="98" spans="1:5" ht="14.25">
       <c r="A98" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B98" s="28">
         <v>2017</v>
@@ -13657,7 +13660,7 @@
     </row>
     <row r="99" spans="1:5" ht="14.25">
       <c r="A99" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B99" s="28">
         <v>2017</v>
@@ -13674,7 +13677,7 @@
     </row>
     <row r="100" spans="1:5" ht="14.25">
       <c r="A100" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B100" s="28">
         <v>2017</v>
@@ -13691,13 +13694,13 @@
     </row>
     <row r="101" spans="1:5" ht="14.25">
       <c r="A101" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B101" s="28">
         <v>2017</v>
       </c>
       <c r="C101" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D101" s="28" t="s">
         <v>354</v>
@@ -13708,7 +13711,7 @@
     </row>
     <row r="102" spans="1:5" ht="14.25">
       <c r="A102" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B102" s="28">
         <v>2017</v>
@@ -13725,13 +13728,13 @@
     </row>
     <row r="103" spans="1:5" ht="14.25">
       <c r="A103" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B103" s="28">
         <v>2017</v>
       </c>
       <c r="C103" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D103" s="28" t="s">
         <v>356</v>
@@ -13742,7 +13745,7 @@
     </row>
     <row r="104" spans="1:5" ht="14.25">
       <c r="A104" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B104" s="28">
         <v>2017</v>
@@ -13759,13 +13762,13 @@
     </row>
     <row r="105" spans="1:5" ht="14.25">
       <c r="A105" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B105" s="28">
         <v>2017</v>
       </c>
       <c r="C105" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D105" s="28" t="s">
         <v>355</v>
@@ -13776,7 +13779,7 @@
     </row>
     <row r="106" spans="1:5" ht="14.25">
       <c r="A106" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B106" s="28">
         <v>2017</v>
@@ -13793,7 +13796,7 @@
     </row>
     <row r="107" spans="1:5" ht="14.25">
       <c r="A107" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B107" s="28">
         <v>2017</v>
@@ -13810,7 +13813,7 @@
     </row>
     <row r="108" spans="1:5" ht="14.25">
       <c r="A108" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B108" s="28">
         <v>2017</v>
@@ -13827,13 +13830,13 @@
     </row>
     <row r="109" spans="1:5" ht="14.25">
       <c r="A109" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B109" s="28">
         <v>2017</v>
       </c>
       <c r="C109" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D109" s="28" t="s">
         <v>357</v>
@@ -13844,7 +13847,7 @@
     </row>
     <row r="110" spans="1:5" ht="14.25">
       <c r="A110" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B110" s="28">
         <v>2016</v>
@@ -13861,13 +13864,13 @@
     </row>
     <row r="111" spans="1:5" ht="14.25">
       <c r="A111" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B111" s="28">
         <v>2016</v>
       </c>
       <c r="C111" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D111" s="28" t="s">
         <v>352</v>
@@ -13878,7 +13881,7 @@
     </row>
     <row r="112" spans="1:5" ht="14.25">
       <c r="A112" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B112" s="28">
         <v>2016</v>
@@ -13895,7 +13898,7 @@
     </row>
     <row r="113" spans="1:5" ht="14.25">
       <c r="A113" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B113" s="28">
         <v>2016</v>
@@ -13912,13 +13915,13 @@
     </row>
     <row r="114" spans="1:5" ht="14.25">
       <c r="A114" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B114" s="28">
         <v>2016</v>
       </c>
       <c r="C114" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D114" s="28" t="s">
         <v>353</v>
@@ -13929,7 +13932,7 @@
     </row>
     <row r="115" spans="1:5" ht="14.25">
       <c r="A115" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B115" s="28">
         <v>2016</v>
@@ -13946,7 +13949,7 @@
     </row>
     <row r="116" spans="1:5" ht="14.25">
       <c r="A116" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B116" s="28">
         <v>2016</v>
@@ -13963,7 +13966,7 @@
     </row>
     <row r="117" spans="1:5" ht="14.25">
       <c r="A117" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B117" s="28">
         <v>2016</v>
@@ -13980,7 +13983,7 @@
     </row>
     <row r="118" spans="1:5" ht="14.25">
       <c r="A118" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B118" s="28">
         <v>2016</v>
@@ -13997,7 +14000,7 @@
     </row>
     <row r="119" spans="1:5" ht="14.25">
       <c r="A119" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B119" s="28">
         <v>2016</v>
@@ -14014,13 +14017,13 @@
     </row>
     <row r="120" spans="1:5" ht="14.25">
       <c r="A120" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B120" s="28">
         <v>2016</v>
       </c>
       <c r="C120" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D120" s="28" t="s">
         <v>354</v>
@@ -14031,13 +14034,13 @@
     </row>
     <row r="121" spans="1:5" ht="14.25">
       <c r="A121" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B121" s="28">
         <v>2016</v>
       </c>
       <c r="C121" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D121" s="28" t="s">
         <v>356</v>
@@ -14048,7 +14051,7 @@
     </row>
     <row r="122" spans="1:5" ht="14.25">
       <c r="A122" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B122" s="28">
         <v>2016</v>
@@ -14065,7 +14068,7 @@
     </row>
     <row r="123" spans="1:5" ht="14.25">
       <c r="A123" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B123" s="28">
         <v>2016</v>
@@ -14082,13 +14085,13 @@
     </row>
     <row r="124" spans="1:5" ht="14.25">
       <c r="A124" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B124" s="28">
         <v>2016</v>
       </c>
       <c r="C124" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D124" s="28" t="s">
         <v>355</v>
@@ -14099,7 +14102,7 @@
     </row>
     <row r="125" spans="1:5" ht="14.25">
       <c r="A125" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B125" s="28">
         <v>2016</v>
@@ -14116,7 +14119,7 @@
     </row>
     <row r="126" spans="1:5" ht="14.25">
       <c r="A126" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B126" s="28">
         <v>2016</v>
@@ -14133,13 +14136,13 @@
     </row>
     <row r="127" spans="1:5" ht="14.25">
       <c r="A127" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B127" s="28">
         <v>2016</v>
       </c>
       <c r="C127" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D127" s="28" t="s">
         <v>357</v>
@@ -14150,7 +14153,7 @@
     </row>
     <row r="128" spans="1:5" ht="14.25">
       <c r="A128" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B128" s="28">
         <v>2015</v>
@@ -14167,13 +14170,13 @@
     </row>
     <row r="129" spans="1:5" ht="14.25">
       <c r="A129" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B129" s="28">
         <v>2015</v>
       </c>
       <c r="C129" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D129" s="28" t="s">
         <v>353</v>
@@ -14184,13 +14187,13 @@
     </row>
     <row r="130" spans="1:5" ht="14.25">
       <c r="A130" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B130" s="28">
         <v>2015</v>
       </c>
       <c r="C130" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D130" s="28" t="s">
         <v>352</v>
@@ -14201,7 +14204,7 @@
     </row>
     <row r="131" spans="1:5" ht="14.25">
       <c r="A131" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B131" s="28">
         <v>2015</v>
@@ -14218,7 +14221,7 @@
     </row>
     <row r="132" spans="1:5" ht="14.25">
       <c r="A132" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B132" s="28">
         <v>2015</v>
@@ -14235,7 +14238,7 @@
     </row>
     <row r="133" spans="1:5" ht="14.25">
       <c r="A133" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B133" s="28">
         <v>2015</v>
@@ -14252,7 +14255,7 @@
     </row>
     <row r="134" spans="1:5" ht="14.25">
       <c r="A134" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B134" s="28">
         <v>2015</v>
@@ -14269,7 +14272,7 @@
     </row>
     <row r="135" spans="1:5" ht="14.25">
       <c r="A135" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B135" s="28">
         <v>2015</v>
@@ -14286,7 +14289,7 @@
     </row>
     <row r="136" spans="1:5" ht="14.25">
       <c r="A136" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B136" s="28">
         <v>2015</v>
@@ -14303,13 +14306,13 @@
     </row>
     <row r="137" spans="1:5" ht="14.25">
       <c r="A137" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B137" s="28">
         <v>2015</v>
       </c>
       <c r="C137" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D137" s="28" t="s">
         <v>354</v>
@@ -14320,13 +14323,13 @@
     </row>
     <row r="138" spans="1:5" ht="14.25">
       <c r="A138" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B138" s="28">
         <v>2015</v>
       </c>
       <c r="C138" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D138" s="28" t="s">
         <v>356</v>
@@ -14337,7 +14340,7 @@
     </row>
     <row r="139" spans="1:5" ht="14.25">
       <c r="A139" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B139" s="28">
         <v>2015</v>
@@ -14354,13 +14357,13 @@
     </row>
     <row r="140" spans="1:5" ht="14.25">
       <c r="A140" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B140" s="28">
         <v>2015</v>
       </c>
       <c r="C140" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D140" s="28" t="s">
         <v>355</v>
@@ -14371,7 +14374,7 @@
     </row>
     <row r="141" spans="1:5" ht="14.25">
       <c r="A141" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B141" s="28">
         <v>2015</v>
@@ -14388,7 +14391,7 @@
     </row>
     <row r="142" spans="1:5" ht="14.25">
       <c r="A142" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B142" s="28">
         <v>2015</v>
@@ -14405,7 +14408,7 @@
     </row>
     <row r="143" spans="1:5" ht="14.25">
       <c r="A143" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B143" s="28">
         <v>2015</v>
@@ -14422,13 +14425,13 @@
     </row>
     <row r="144" spans="1:5" ht="14.25">
       <c r="A144" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B144" s="28">
         <v>2015</v>
       </c>
       <c r="C144" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D144" s="28" t="s">
         <v>357</v>
@@ -14439,7 +14442,7 @@
     </row>
     <row r="145" spans="1:5" ht="14.25">
       <c r="A145" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B145" s="28">
         <v>2015</v>
@@ -14456,7 +14459,7 @@
     </row>
     <row r="146" spans="1:5" ht="14.25">
       <c r="A146" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B146" s="28">
         <v>2014</v>
@@ -14473,13 +14476,13 @@
     </row>
     <row r="147" spans="1:5" ht="14.25">
       <c r="A147" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B147" s="28">
         <v>2014</v>
       </c>
       <c r="C147" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D147" s="28" t="s">
         <v>353</v>
@@ -14490,7 +14493,7 @@
     </row>
     <row r="148" spans="1:5" ht="14.25">
       <c r="A148" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B148" s="28">
         <v>2014</v>
@@ -14507,13 +14510,13 @@
     </row>
     <row r="149" spans="1:5" ht="14.25">
       <c r="A149" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B149" s="28">
         <v>2014</v>
       </c>
       <c r="C149" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D149" s="28" t="s">
         <v>352</v>
@@ -14524,7 +14527,7 @@
     </row>
     <row r="150" spans="1:5" ht="14.25">
       <c r="A150" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B150" s="28">
         <v>2014</v>
@@ -14541,7 +14544,7 @@
     </row>
     <row r="151" spans="1:5" ht="14.25">
       <c r="A151" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B151" s="28">
         <v>2014</v>
@@ -14558,7 +14561,7 @@
     </row>
     <row r="152" spans="1:5" ht="14.25">
       <c r="A152" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B152" s="28">
         <v>2014</v>
@@ -14575,7 +14578,7 @@
     </row>
     <row r="153" spans="1:5" ht="14.25">
       <c r="A153" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B153" s="28">
         <v>2014</v>
@@ -14592,7 +14595,7 @@
     </row>
     <row r="154" spans="1:5" ht="14.25">
       <c r="A154" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B154" s="28">
         <v>2014</v>
@@ -14609,13 +14612,13 @@
     </row>
     <row r="155" spans="1:5" ht="14.25">
       <c r="A155" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B155" s="28">
         <v>2014</v>
       </c>
       <c r="C155" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D155" s="28" t="s">
         <v>354</v>
@@ -14626,13 +14629,13 @@
     </row>
     <row r="156" spans="1:5" ht="14.25">
       <c r="A156" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B156" s="28">
         <v>2014</v>
       </c>
       <c r="C156" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D156" s="28" t="s">
         <v>356</v>
@@ -14643,7 +14646,7 @@
     </row>
     <row r="157" spans="1:5" ht="14.25">
       <c r="A157" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B157" s="28">
         <v>2014</v>
@@ -14660,13 +14663,13 @@
     </row>
     <row r="158" spans="1:5" ht="14.25">
       <c r="A158" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B158" s="28">
         <v>2014</v>
       </c>
       <c r="C158" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D158" s="28" t="s">
         <v>355</v>
@@ -14677,7 +14680,7 @@
     </row>
     <row r="159" spans="1:5" ht="14.25">
       <c r="A159" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B159" s="28">
         <v>2014</v>
@@ -14694,7 +14697,7 @@
     </row>
     <row r="160" spans="1:5" ht="14.25">
       <c r="A160" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B160" s="28">
         <v>2014</v>
@@ -14711,7 +14714,7 @@
     </row>
     <row r="161" spans="1:5" ht="14.25">
       <c r="A161" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B161" s="28">
         <v>2014</v>
@@ -14728,13 +14731,13 @@
     </row>
     <row r="162" spans="1:5" ht="14.25">
       <c r="A162" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B162" s="28">
         <v>2014</v>
       </c>
       <c r="C162" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D162" s="28" t="s">
         <v>357</v>
@@ -14745,7 +14748,7 @@
     </row>
     <row r="163" spans="1:5" ht="14.25">
       <c r="A163" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B163" s="28">
         <v>2014</v>
@@ -14762,7 +14765,7 @@
     </row>
     <row r="164" spans="1:5" ht="14.25">
       <c r="A164" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B164" s="28">
         <v>2013</v>
@@ -14779,13 +14782,13 @@
     </row>
     <row r="165" spans="1:5" ht="14.25">
       <c r="A165" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B165" s="28">
         <v>2013</v>
       </c>
       <c r="C165" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D165" s="28" t="s">
         <v>353</v>
@@ -14796,7 +14799,7 @@
     </row>
     <row r="166" spans="1:5" ht="14.25">
       <c r="A166" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B166" s="28">
         <v>2013</v>
@@ -14813,7 +14816,7 @@
     </row>
     <row r="167" spans="1:5" ht="14.25">
       <c r="A167" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B167" s="28">
         <v>2013</v>
@@ -14830,7 +14833,7 @@
     </row>
     <row r="168" spans="1:5" ht="14.25">
       <c r="A168" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B168" s="28">
         <v>2013</v>
@@ -14847,13 +14850,13 @@
     </row>
     <row r="169" spans="1:5" ht="14.25">
       <c r="A169" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B169" s="28">
         <v>2013</v>
       </c>
       <c r="C169" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D169" s="28" t="s">
         <v>352</v>
@@ -14864,7 +14867,7 @@
     </row>
     <row r="170" spans="1:5" ht="14.25">
       <c r="A170" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B170" s="28">
         <v>2013</v>
@@ -14881,13 +14884,13 @@
     </row>
     <row r="171" spans="1:5" ht="14.25">
       <c r="A171" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B171" s="28">
         <v>2013</v>
       </c>
       <c r="C171" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D171" s="28" t="s">
         <v>354</v>
@@ -14898,7 +14901,7 @@
     </row>
     <row r="172" spans="1:5" ht="14.25">
       <c r="A172" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B172" s="28">
         <v>2013</v>
@@ -14915,7 +14918,7 @@
     </row>
     <row r="173" spans="1:5" ht="14.25">
       <c r="A173" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B173" s="28">
         <v>2013</v>
@@ -14932,13 +14935,13 @@
     </row>
     <row r="174" spans="1:5" ht="14.25">
       <c r="A174" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B174" s="28">
         <v>2013</v>
       </c>
       <c r="C174" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D174" s="28" t="s">
         <v>356</v>
@@ -14949,7 +14952,7 @@
     </row>
     <row r="175" spans="1:5" ht="14.25">
       <c r="A175" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B175" s="28">
         <v>2013</v>
@@ -14966,7 +14969,7 @@
     </row>
     <row r="176" spans="1:5" ht="14.25">
       <c r="A176" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B176" s="28">
         <v>2013</v>
@@ -14983,13 +14986,13 @@
     </row>
     <row r="177" spans="1:5" ht="14.25">
       <c r="A177" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B177" s="28">
         <v>2013</v>
       </c>
       <c r="C177" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D177" s="28" t="s">
         <v>355</v>
@@ -15000,13 +15003,13 @@
     </row>
     <row r="178" spans="1:5" ht="14.25">
       <c r="A178" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B178" s="28">
         <v>2013</v>
       </c>
       <c r="C178" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D178" s="28" t="s">
         <v>357</v>
@@ -15017,7 +15020,7 @@
     </row>
     <row r="179" spans="1:5" ht="14.25">
       <c r="A179" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B179" s="28">
         <v>2013</v>
@@ -15034,7 +15037,7 @@
     </row>
     <row r="180" spans="1:5" ht="14.25">
       <c r="A180" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B180" s="28">
         <v>2013</v>
@@ -15051,7 +15054,7 @@
     </row>
     <row r="181" spans="1:5" ht="14.25">
       <c r="A181" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B181" s="28">
         <v>2013</v>
@@ -15068,7 +15071,7 @@
     </row>
     <row r="182" spans="1:5" ht="14.25">
       <c r="A182" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B182" s="28">
         <v>2012</v>
@@ -15085,7 +15088,7 @@
     </row>
     <row r="183" spans="1:5" ht="14.25">
       <c r="A183" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B183" s="28">
         <v>2012</v>
@@ -15102,7 +15105,7 @@
     </row>
     <row r="184" spans="1:5" ht="14.25">
       <c r="A184" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B184" s="28">
         <v>2012</v>
@@ -15119,13 +15122,13 @@
     </row>
     <row r="185" spans="1:5" ht="14.25">
       <c r="A185" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B185" s="28">
         <v>2012</v>
       </c>
       <c r="C185" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D185" s="28" t="s">
         <v>353</v>
@@ -15136,7 +15139,7 @@
     </row>
     <row r="186" spans="1:5" ht="14.25">
       <c r="A186" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B186" s="28">
         <v>2012</v>
@@ -15153,13 +15156,13 @@
     </row>
     <row r="187" spans="1:5" ht="14.25">
       <c r="A187" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B187" s="28">
         <v>2012</v>
       </c>
       <c r="C187" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D187" s="28" t="s">
         <v>352</v>
@@ -15170,7 +15173,7 @@
     </row>
     <row r="188" spans="1:5" ht="14.25">
       <c r="A188" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B188" s="28">
         <v>2012</v>
@@ -15187,13 +15190,13 @@
     </row>
     <row r="189" spans="1:5" ht="14.25">
       <c r="A189" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B189" s="28">
         <v>2012</v>
       </c>
       <c r="C189" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D189" s="28" t="s">
         <v>354</v>
@@ -15204,7 +15207,7 @@
     </row>
     <row r="190" spans="1:5" ht="14.25">
       <c r="A190" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B190" s="28">
         <v>2012</v>
@@ -15221,7 +15224,7 @@
     </row>
     <row r="191" spans="1:5" ht="14.25">
       <c r="A191" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B191" s="28">
         <v>2012</v>
@@ -15238,7 +15241,7 @@
     </row>
     <row r="192" spans="1:5" ht="14.25">
       <c r="A192" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B192" s="28">
         <v>2012</v>
@@ -15255,7 +15258,7 @@
     </row>
     <row r="193" spans="1:5" ht="14.25">
       <c r="A193" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B193" s="28">
         <v>2012</v>
@@ -15272,13 +15275,13 @@
     </row>
     <row r="194" spans="1:5" ht="14.25">
       <c r="A194" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B194" s="28">
         <v>2012</v>
       </c>
       <c r="C194" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D194" s="28" t="s">
         <v>356</v>
@@ -15289,13 +15292,13 @@
     </row>
     <row r="195" spans="1:5" ht="14.25">
       <c r="A195" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B195" s="28">
         <v>2012</v>
       </c>
       <c r="C195" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D195" s="28" t="s">
         <v>355</v>
@@ -15306,13 +15309,13 @@
     </row>
     <row r="196" spans="1:5" ht="14.25">
       <c r="A196" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B196" s="28">
         <v>2012</v>
       </c>
       <c r="C196" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D196" s="28" t="s">
         <v>357</v>
@@ -15323,7 +15326,7 @@
     </row>
     <row r="197" spans="1:5" ht="14.25">
       <c r="A197" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B197" s="28">
         <v>2012</v>
@@ -15340,7 +15343,7 @@
     </row>
     <row r="198" spans="1:5" ht="14.25">
       <c r="A198" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B198" s="28">
         <v>2012</v>
@@ -15357,7 +15360,7 @@
     </row>
     <row r="199" spans="1:5" ht="14.25">
       <c r="A199" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B199" s="28">
         <v>2012</v>
@@ -15374,7 +15377,7 @@
     </row>
     <row r="200" spans="1:5" ht="14.25">
       <c r="A200" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B200" s="28">
         <v>2011</v>
@@ -15391,7 +15394,7 @@
     </row>
     <row r="201" spans="1:5" ht="14.25">
       <c r="A201" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B201" s="28">
         <v>2011</v>
@@ -15408,7 +15411,7 @@
     </row>
     <row r="202" spans="1:5" ht="14.25">
       <c r="A202" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B202" s="28">
         <v>2011</v>
@@ -15425,13 +15428,13 @@
     </row>
     <row r="203" spans="1:5" ht="14.25">
       <c r="A203" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B203" s="28">
         <v>2011</v>
       </c>
       <c r="C203" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D203" s="28" t="s">
         <v>353</v>
@@ -15442,7 +15445,7 @@
     </row>
     <row r="204" spans="1:5" ht="14.25">
       <c r="A204" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B204" s="28">
         <v>2011</v>
@@ -15459,13 +15462,13 @@
     </row>
     <row r="205" spans="1:5" ht="14.25">
       <c r="A205" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B205" s="28">
         <v>2011</v>
       </c>
       <c r="C205" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D205" s="28" t="s">
         <v>352</v>
@@ -15476,13 +15479,13 @@
     </row>
     <row r="206" spans="1:5" ht="14.25">
       <c r="A206" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B206" s="28">
         <v>2011</v>
       </c>
       <c r="C206" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D206" s="28" t="s">
         <v>354</v>
@@ -15493,7 +15496,7 @@
     </row>
     <row r="207" spans="1:5" ht="14.25">
       <c r="A207" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B207" s="28">
         <v>2011</v>
@@ -15510,7 +15513,7 @@
     </row>
     <row r="208" spans="1:5" ht="14.25">
       <c r="A208" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B208" s="28">
         <v>2011</v>
@@ -15527,7 +15530,7 @@
     </row>
     <row r="209" spans="1:5" ht="14.25">
       <c r="A209" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B209" s="28">
         <v>2011</v>
@@ -15544,7 +15547,7 @@
     </row>
     <row r="210" spans="1:5" ht="14.25">
       <c r="A210" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B210" s="28">
         <v>2011</v>
@@ -15561,7 +15564,7 @@
     </row>
     <row r="211" spans="1:5" ht="14.25">
       <c r="A211" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B211" s="28">
         <v>2011</v>
@@ -15578,13 +15581,13 @@
     </row>
     <row r="212" spans="1:5" ht="14.25">
       <c r="A212" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B212" s="28">
         <v>2011</v>
       </c>
       <c r="C212" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D212" s="28" t="s">
         <v>356</v>
@@ -15595,13 +15598,13 @@
     </row>
     <row r="213" spans="1:5" ht="14.25">
       <c r="A213" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B213" s="28">
         <v>2011</v>
       </c>
       <c r="C213" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D213" s="28" t="s">
         <v>355</v>
@@ -15612,13 +15615,13 @@
     </row>
     <row r="214" spans="1:5" ht="14.25">
       <c r="A214" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B214" s="28">
         <v>2011</v>
       </c>
       <c r="C214" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D214" s="28" t="s">
         <v>357</v>
@@ -15629,7 +15632,7 @@
     </row>
     <row r="215" spans="1:5" ht="14.25">
       <c r="A215" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B215" s="28">
         <v>2011</v>
@@ -15646,7 +15649,7 @@
     </row>
     <row r="216" spans="1:5" ht="14.25">
       <c r="A216" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B216" s="28">
         <v>2011</v>
@@ -15663,7 +15666,7 @@
     </row>
     <row r="217" spans="1:5" ht="14.25">
       <c r="A217" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B217" s="28">
         <v>2011</v>
@@ -15680,7 +15683,7 @@
     </row>
     <row r="218" spans="1:5" ht="14.25">
       <c r="A218" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B218" s="28">
         <v>2010</v>
@@ -15697,7 +15700,7 @@
     </row>
     <row r="219" spans="1:5" ht="14.25">
       <c r="A219" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B219" s="28">
         <v>2010</v>
@@ -15714,7 +15717,7 @@
     </row>
     <row r="220" spans="1:5" ht="14.25">
       <c r="A220" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B220" s="28">
         <v>2010</v>
@@ -15731,13 +15734,13 @@
     </row>
     <row r="221" spans="1:5" ht="14.25">
       <c r="A221" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B221" s="28">
         <v>2010</v>
       </c>
       <c r="C221" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D221" s="28" t="s">
         <v>353</v>
@@ -15748,13 +15751,13 @@
     </row>
     <row r="222" spans="1:5" ht="14.25">
       <c r="A222" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B222" s="28">
         <v>2010</v>
       </c>
       <c r="C222" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D222" s="28" t="s">
         <v>354</v>
@@ -15765,7 +15768,7 @@
     </row>
     <row r="223" spans="1:5" ht="14.25">
       <c r="A223" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B223" s="28">
         <v>2010</v>
@@ -15782,7 +15785,7 @@
     </row>
     <row r="224" spans="1:5" ht="14.25">
       <c r="A224" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B224" s="28">
         <v>2010</v>
@@ -15799,13 +15802,13 @@
     </row>
     <row r="225" spans="1:5" ht="14.25">
       <c r="A225" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B225" s="28">
         <v>2010</v>
       </c>
       <c r="C225" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D225" s="28" t="s">
         <v>352</v>
@@ -15816,7 +15819,7 @@
     </row>
     <row r="226" spans="1:5" ht="14.25">
       <c r="A226" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B226" s="28">
         <v>2010</v>
@@ -15833,7 +15836,7 @@
     </row>
     <row r="227" spans="1:5" ht="14.25">
       <c r="A227" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B227" s="28">
         <v>2010</v>
@@ -15850,7 +15853,7 @@
     </row>
     <row r="228" spans="1:5" ht="14.25">
       <c r="A228" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B228" s="28">
         <v>2010</v>
@@ -15867,7 +15870,7 @@
     </row>
     <row r="229" spans="1:5" ht="14.25">
       <c r="A229" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B229" s="28">
         <v>2010</v>
@@ -15884,13 +15887,13 @@
     </row>
     <row r="230" spans="1:5" ht="14.25">
       <c r="A230" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B230" s="28">
         <v>2010</v>
       </c>
       <c r="C230" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D230" s="28" t="s">
         <v>356</v>
@@ -15901,13 +15904,13 @@
     </row>
     <row r="231" spans="1:5" ht="14.25">
       <c r="A231" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B231" s="28">
         <v>2010</v>
       </c>
       <c r="C231" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D231" s="28" t="s">
         <v>355</v>
@@ -15918,13 +15921,13 @@
     </row>
     <row r="232" spans="1:5" ht="14.25">
       <c r="A232" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B232" s="28">
         <v>2010</v>
       </c>
       <c r="C232" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D232" s="28" t="s">
         <v>357</v>
@@ -15935,7 +15938,7 @@
     </row>
     <row r="233" spans="1:5" ht="14.25">
       <c r="A233" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B233" s="28">
         <v>2010</v>
@@ -15952,7 +15955,7 @@
     </row>
     <row r="234" spans="1:5" ht="14.25">
       <c r="A234" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B234" s="28">
         <v>2010</v>
@@ -15969,7 +15972,7 @@
     </row>
     <row r="235" spans="1:5" ht="14.25">
       <c r="A235" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B235" s="28">
         <v>2010</v>
@@ -15986,7 +15989,7 @@
     </row>
     <row r="236" spans="1:5" ht="14.25">
       <c r="A236" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B236" s="28">
         <v>2009</v>
@@ -16003,7 +16006,7 @@
     </row>
     <row r="237" spans="1:5" ht="14.25">
       <c r="A237" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B237" s="28">
         <v>2009</v>
@@ -16020,7 +16023,7 @@
     </row>
     <row r="238" spans="1:5" ht="14.25">
       <c r="A238" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B238" s="28">
         <v>2009</v>
@@ -16037,13 +16040,13 @@
     </row>
     <row r="239" spans="1:5" ht="14.25">
       <c r="A239" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B239" s="28">
         <v>2009</v>
       </c>
       <c r="C239" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D239" s="28" t="s">
         <v>354</v>
@@ -16054,13 +16057,13 @@
     </row>
     <row r="240" spans="1:5" ht="14.25">
       <c r="A240" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B240" s="28">
         <v>2009</v>
       </c>
       <c r="C240" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D240" s="28" t="s">
         <v>353</v>
@@ -16071,7 +16074,7 @@
     </row>
     <row r="241" spans="1:5" ht="14.25">
       <c r="A241" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B241" s="28">
         <v>2009</v>
@@ -16088,7 +16091,7 @@
     </row>
     <row r="242" spans="1:5" ht="14.25">
       <c r="A242" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B242" s="28">
         <v>2009</v>
@@ -16105,7 +16108,7 @@
     </row>
     <row r="243" spans="1:5" ht="14.25">
       <c r="A243" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B243" s="28">
         <v>2009</v>
@@ -16122,13 +16125,13 @@
     </row>
     <row r="244" spans="1:5" ht="14.25">
       <c r="A244" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B244" s="28">
         <v>2009</v>
       </c>
       <c r="C244" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D244" s="28" t="s">
         <v>352</v>
@@ -16139,7 +16142,7 @@
     </row>
     <row r="245" spans="1:5" ht="14.25">
       <c r="A245" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B245" s="28">
         <v>2009</v>
@@ -16156,7 +16159,7 @@
     </row>
     <row r="246" spans="1:5" ht="14.25">
       <c r="A246" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B246" s="28">
         <v>2009</v>
@@ -16173,7 +16176,7 @@
     </row>
     <row r="247" spans="1:5" ht="14.25">
       <c r="A247" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B247" s="28">
         <v>2009</v>
@@ -16190,13 +16193,13 @@
     </row>
     <row r="248" spans="1:5" ht="14.25">
       <c r="A248" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B248" s="28">
         <v>2009</v>
       </c>
       <c r="C248" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D248" s="28" t="s">
         <v>357</v>
@@ -16207,13 +16210,13 @@
     </row>
     <row r="249" spans="1:5" ht="14.25">
       <c r="A249" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B249" s="28">
         <v>2009</v>
       </c>
       <c r="C249" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D249" s="28" t="s">
         <v>355</v>
@@ -16224,13 +16227,13 @@
     </row>
     <row r="250" spans="1:5" ht="14.25">
       <c r="A250" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B250" s="28">
         <v>2009</v>
       </c>
       <c r="C250" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D250" s="28" t="s">
         <v>356</v>
@@ -16241,7 +16244,7 @@
     </row>
     <row r="251" spans="1:5" ht="14.25">
       <c r="A251" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B251" s="28">
         <v>2009</v>
@@ -16258,7 +16261,7 @@
     </row>
     <row r="252" spans="1:5" ht="14.25">
       <c r="A252" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B252" s="28">
         <v>2009</v>
@@ -16275,7 +16278,7 @@
     </row>
     <row r="253" spans="1:5" ht="14.25">
       <c r="A253" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B253" s="28">
         <v>2009</v>
@@ -16292,7 +16295,7 @@
     </row>
     <row r="254" spans="1:5" ht="14.25">
       <c r="A254" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B254" s="28">
         <v>2008</v>
@@ -16309,7 +16312,7 @@
     </row>
     <row r="255" spans="1:5" ht="14.25">
       <c r="A255" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B255" s="28">
         <v>2008</v>
@@ -16326,7 +16329,7 @@
     </row>
     <row r="256" spans="1:5" ht="14.25">
       <c r="A256" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B256" s="28">
         <v>2008</v>
@@ -16343,7 +16346,7 @@
     </row>
     <row r="257" spans="1:5" ht="14.25">
       <c r="A257" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B257" s="28">
         <v>2008</v>
@@ -16360,7 +16363,7 @@
     </row>
     <row r="258" spans="1:5" ht="14.25">
       <c r="A258" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B258" s="28">
         <v>2008</v>
@@ -16377,13 +16380,13 @@
     </row>
     <row r="259" spans="1:5" ht="14.25">
       <c r="A259" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B259" s="28">
         <v>2008</v>
       </c>
       <c r="C259" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D259" s="28" t="s">
         <v>354</v>
@@ -16394,13 +16397,13 @@
     </row>
     <row r="260" spans="1:5" ht="14.25">
       <c r="A260" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B260" s="28">
         <v>2008</v>
       </c>
       <c r="C260" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D260" s="28" t="s">
         <v>353</v>
@@ -16411,7 +16414,7 @@
     </row>
     <row r="261" spans="1:5" ht="14.25">
       <c r="A261" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B261" s="28">
         <v>2008</v>
@@ -16428,7 +16431,7 @@
     </row>
     <row r="262" spans="1:5" ht="14.25">
       <c r="A262" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B262" s="28">
         <v>2008</v>
@@ -16445,13 +16448,13 @@
     </row>
     <row r="263" spans="1:5" ht="14.25">
       <c r="A263" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B263" s="28">
         <v>2008</v>
       </c>
       <c r="C263" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D263" s="28" t="s">
         <v>357</v>
@@ -16462,13 +16465,13 @@
     </row>
     <row r="264" spans="1:5" ht="14.25">
       <c r="A264" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B264" s="28">
         <v>2008</v>
       </c>
       <c r="C264" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D264" s="28" t="s">
         <v>352</v>
@@ -16479,7 +16482,7 @@
     </row>
     <row r="265" spans="1:5" ht="14.25">
       <c r="A265" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B265" s="28">
         <v>2008</v>
@@ -16496,7 +16499,7 @@
     </row>
     <row r="266" spans="1:5" ht="14.25">
       <c r="A266" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B266" s="28">
         <v>2008</v>
@@ -16513,13 +16516,13 @@
     </row>
     <row r="267" spans="1:5" ht="14.25">
       <c r="A267" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B267" s="28">
         <v>2008</v>
       </c>
       <c r="C267" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D267" s="28" t="s">
         <v>355</v>
@@ -16530,13 +16533,13 @@
     </row>
     <row r="268" spans="1:5" ht="14.25">
       <c r="A268" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B268" s="28">
         <v>2008</v>
       </c>
       <c r="C268" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D268" s="28" t="s">
         <v>356</v>
@@ -16547,7 +16550,7 @@
     </row>
     <row r="269" spans="1:5" ht="14.25">
       <c r="A269" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B269" s="28">
         <v>2008</v>
@@ -16564,7 +16567,7 @@
     </row>
     <row r="270" spans="1:5" ht="14.25">
       <c r="A270" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B270" s="28">
         <v>2008</v>
@@ -16581,7 +16584,7 @@
     </row>
     <row r="271" spans="1:5" ht="14.25">
       <c r="A271" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B271" s="28">
         <v>2008</v>
@@ -16598,7 +16601,7 @@
     </row>
     <row r="272" spans="1:5" ht="14.25">
       <c r="A272" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B272" s="28">
         <v>2007</v>
@@ -16615,7 +16618,7 @@
     </row>
     <row r="273" spans="1:5" ht="14.25">
       <c r="A273" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B273" s="28">
         <v>2007</v>
@@ -16632,7 +16635,7 @@
     </row>
     <row r="274" spans="1:5" ht="14.25">
       <c r="A274" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B274" s="28">
         <v>2007</v>
@@ -16649,7 +16652,7 @@
     </row>
     <row r="275" spans="1:5" ht="14.25">
       <c r="A275" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B275" s="28">
         <v>2007</v>
@@ -16666,7 +16669,7 @@
     </row>
     <row r="276" spans="1:5" ht="14.25">
       <c r="A276" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B276" s="28">
         <v>2007</v>
@@ -16683,13 +16686,13 @@
     </row>
     <row r="277" spans="1:5" ht="14.25">
       <c r="A277" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B277" s="28">
         <v>2007</v>
       </c>
       <c r="C277" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D277" s="28" t="s">
         <v>354</v>
@@ -16700,13 +16703,13 @@
     </row>
     <row r="278" spans="1:5" ht="14.25">
       <c r="A278" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B278" s="28">
         <v>2007</v>
       </c>
       <c r="C278" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D278" s="28" t="s">
         <v>353</v>
@@ -16717,7 +16720,7 @@
     </row>
     <row r="279" spans="1:5" ht="14.25">
       <c r="A279" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B279" s="28">
         <v>2007</v>
@@ -16734,13 +16737,13 @@
     </row>
     <row r="280" spans="1:5" ht="14.25">
       <c r="A280" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B280" s="28">
         <v>2007</v>
       </c>
       <c r="C280" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D280" s="28" t="s">
         <v>357</v>
@@ -16751,7 +16754,7 @@
     </row>
     <row r="281" spans="1:5" ht="14.25">
       <c r="A281" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B281" s="28">
         <v>2007</v>
@@ -16768,13 +16771,13 @@
     </row>
     <row r="282" spans="1:5" ht="14.25">
       <c r="A282" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B282" s="28">
         <v>2007</v>
       </c>
       <c r="C282" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D282" s="28" t="s">
         <v>352</v>
@@ -16785,13 +16788,13 @@
     </row>
     <row r="283" spans="1:5" ht="14.25">
       <c r="A283" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B283" s="28">
         <v>2007</v>
       </c>
       <c r="C283" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D283" s="28" t="s">
         <v>355</v>
@@ -16802,13 +16805,13 @@
     </row>
     <row r="284" spans="1:5" ht="14.25">
       <c r="A284" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B284" s="28">
         <v>2007</v>
       </c>
       <c r="C284" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D284" s="28" t="s">
         <v>356</v>
@@ -16819,7 +16822,7 @@
     </row>
     <row r="285" spans="1:5" ht="14.25">
       <c r="A285" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B285" s="28">
         <v>2007</v>
@@ -16836,7 +16839,7 @@
     </row>
     <row r="286" spans="1:5" ht="14.25">
       <c r="A286" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B286" s="28">
         <v>2007</v>
@@ -16853,7 +16856,7 @@
     </row>
     <row r="287" spans="1:5" ht="14.25">
       <c r="A287" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B287" s="28">
         <v>2007</v>
@@ -16870,7 +16873,7 @@
     </row>
     <row r="288" spans="1:5" ht="14.25">
       <c r="A288" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B288" s="28">
         <v>2007</v>
@@ -16887,7 +16890,7 @@
     </row>
     <row r="289" spans="1:5" ht="14.25">
       <c r="A289" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B289" s="28">
         <v>2007</v>
@@ -16904,7 +16907,7 @@
     </row>
     <row r="290" spans="1:5" ht="14.25">
       <c r="A290" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B290" s="28">
         <v>2006</v>
@@ -16921,7 +16924,7 @@
     </row>
     <row r="291" spans="1:5" ht="14.25">
       <c r="A291" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B291" s="28">
         <v>2006</v>
@@ -16938,7 +16941,7 @@
     </row>
     <row r="292" spans="1:5" ht="14.25">
       <c r="A292" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B292" s="28">
         <v>2006</v>
@@ -16955,7 +16958,7 @@
     </row>
     <row r="293" spans="1:5" ht="14.25">
       <c r="A293" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B293" s="28">
         <v>2006</v>
@@ -16972,7 +16975,7 @@
     </row>
     <row r="294" spans="1:5" ht="14.25">
       <c r="A294" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B294" s="28">
         <v>2006</v>
@@ -16989,13 +16992,13 @@
     </row>
     <row r="295" spans="1:5" ht="14.25">
       <c r="A295" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B295" s="28">
         <v>2006</v>
       </c>
       <c r="C295" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D295" s="28" t="s">
         <v>354</v>
@@ -17006,13 +17009,13 @@
     </row>
     <row r="296" spans="1:5" ht="14.25">
       <c r="A296" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B296" s="28">
         <v>2006</v>
       </c>
       <c r="C296" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D296" s="28" t="s">
         <v>357</v>
@@ -17023,13 +17026,13 @@
     </row>
     <row r="297" spans="1:5" ht="14.25">
       <c r="A297" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B297" s="28">
         <v>2006</v>
       </c>
       <c r="C297" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D297" s="28" t="s">
         <v>353</v>
@@ -17040,7 +17043,7 @@
     </row>
     <row r="298" spans="1:5" ht="14.25">
       <c r="A298" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B298" s="28">
         <v>2006</v>
@@ -17057,13 +17060,13 @@
     </row>
     <row r="299" spans="1:5" ht="14.25">
       <c r="A299" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B299" s="28">
         <v>2006</v>
       </c>
       <c r="C299" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D299" s="28" t="s">
         <v>355</v>
@@ -17074,7 +17077,7 @@
     </row>
     <row r="300" spans="1:5" ht="14.25">
       <c r="A300" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B300" s="28">
         <v>2006</v>
@@ -17091,13 +17094,13 @@
     </row>
     <row r="301" spans="1:5" ht="14.25">
       <c r="A301" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B301" s="28">
         <v>2006</v>
       </c>
       <c r="C301" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D301" s="28" t="s">
         <v>356</v>
@@ -17108,7 +17111,7 @@
     </row>
     <row r="302" spans="1:5" ht="14.25">
       <c r="A302" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B302" s="28">
         <v>2006</v>
@@ -17125,13 +17128,13 @@
     </row>
     <row r="303" spans="1:5" ht="14.25">
       <c r="A303" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B303" s="28">
         <v>2006</v>
       </c>
       <c r="C303" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D303" s="28" t="s">
         <v>352</v>
@@ -17142,7 +17145,7 @@
     </row>
     <row r="304" spans="1:5" ht="14.25">
       <c r="A304" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B304" s="28">
         <v>2006</v>
@@ -17159,7 +17162,7 @@
     </row>
     <row r="305" spans="1:5" ht="14.25">
       <c r="A305" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B305" s="28">
         <v>2006</v>
@@ -17176,7 +17179,7 @@
     </row>
     <row r="306" spans="1:5" ht="14.25">
       <c r="A306" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B306" s="28">
         <v>2006</v>
@@ -17193,7 +17196,7 @@
     </row>
     <row r="307" spans="1:5" ht="14.25">
       <c r="A307" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B307" s="28">
         <v>2006</v>
@@ -17210,7 +17213,7 @@
     </row>
     <row r="308" spans="1:5" ht="14.25">
       <c r="A308" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B308" s="28">
         <v>2005</v>
@@ -17227,7 +17230,7 @@
     </row>
     <row r="309" spans="1:5" ht="14.25">
       <c r="A309" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B309" s="28">
         <v>2005</v>
@@ -17244,7 +17247,7 @@
     </row>
     <row r="310" spans="1:5" ht="14.25">
       <c r="A310" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B310" s="28">
         <v>2005</v>
@@ -17261,7 +17264,7 @@
     </row>
     <row r="311" spans="1:5" ht="14.25">
       <c r="A311" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B311" s="28">
         <v>2005</v>
@@ -17278,7 +17281,7 @@
     </row>
     <row r="312" spans="1:5" ht="14.25">
       <c r="A312" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B312" s="28">
         <v>2005</v>
@@ -17295,13 +17298,13 @@
     </row>
     <row r="313" spans="1:5" ht="14.25">
       <c r="A313" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B313" s="28">
         <v>2005</v>
       </c>
       <c r="C313" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D313" s="28" t="s">
         <v>354</v>
@@ -17312,13 +17315,13 @@
     </row>
     <row r="314" spans="1:5" ht="14.25">
       <c r="A314" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B314" s="28">
         <v>2005</v>
       </c>
       <c r="C314" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D314" s="28" t="s">
         <v>357</v>
@@ -17329,7 +17332,7 @@
     </row>
     <row r="315" spans="1:5" ht="14.25">
       <c r="A315" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B315" s="28">
         <v>2005</v>
@@ -17346,13 +17349,13 @@
     </row>
     <row r="316" spans="1:5" ht="14.25">
       <c r="A316" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B316" s="28">
         <v>2005</v>
       </c>
       <c r="C316" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D316" s="28" t="s">
         <v>353</v>
@@ -17363,13 +17366,13 @@
     </row>
     <row r="317" spans="1:5" ht="14.25">
       <c r="A317" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B317" s="28">
         <v>2005</v>
       </c>
       <c r="C317" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D317" s="28" t="s">
         <v>355</v>
@@ -17380,7 +17383,7 @@
     </row>
     <row r="318" spans="1:5" ht="14.25">
       <c r="A318" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B318" s="28">
         <v>2005</v>
@@ -17397,13 +17400,13 @@
     </row>
     <row r="319" spans="1:5" ht="14.25">
       <c r="A319" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B319" s="28">
         <v>2005</v>
       </c>
       <c r="C319" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D319" s="28" t="s">
         <v>356</v>
@@ -17414,7 +17417,7 @@
     </row>
     <row r="320" spans="1:5" ht="14.25">
       <c r="A320" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B320" s="28">
         <v>2005</v>
@@ -17431,13 +17434,13 @@
     </row>
     <row r="321" spans="1:5" ht="14.25">
       <c r="A321" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B321" s="28">
         <v>2005</v>
       </c>
       <c r="C321" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D321" s="28" t="s">
         <v>352</v>
@@ -17448,7 +17451,7 @@
     </row>
     <row r="322" spans="1:5" ht="14.25">
       <c r="A322" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B322" s="28">
         <v>2005</v>
@@ -17465,7 +17468,7 @@
     </row>
     <row r="323" spans="1:5" ht="14.25">
       <c r="A323" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B323" s="28">
         <v>2005</v>
@@ -17482,7 +17485,7 @@
     </row>
     <row r="324" spans="1:5" ht="14.25">
       <c r="A324" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B324" s="28">
         <v>2005</v>
@@ -17499,7 +17502,7 @@
     </row>
     <row r="325" spans="1:5" ht="14.25">
       <c r="A325" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B325" s="28">
         <v>2005</v>
@@ -17516,7 +17519,7 @@
     </row>
     <row r="326" spans="1:5" ht="14.25">
       <c r="A326" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B326" s="28">
         <v>2004</v>
@@ -17533,7 +17536,7 @@
     </row>
     <row r="327" spans="1:5" ht="14.25">
       <c r="A327" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B327" s="28">
         <v>2004</v>
@@ -17550,7 +17553,7 @@
     </row>
     <row r="328" spans="1:5" ht="14.25">
       <c r="A328" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B328" s="28">
         <v>2004</v>
@@ -17567,7 +17570,7 @@
     </row>
     <row r="329" spans="1:5" ht="14.25">
       <c r="A329" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B329" s="28">
         <v>2004</v>
@@ -17584,7 +17587,7 @@
     </row>
     <row r="330" spans="1:5" ht="14.25">
       <c r="A330" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B330" s="28">
         <v>2004</v>
@@ -17601,13 +17604,13 @@
     </row>
     <row r="331" spans="1:5" ht="14.25">
       <c r="A331" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B331" s="28">
         <v>2004</v>
       </c>
       <c r="C331" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D331" s="28" t="s">
         <v>354</v>
@@ -17618,13 +17621,13 @@
     </row>
     <row r="332" spans="1:5" ht="14.25">
       <c r="A332" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B332" s="28">
         <v>2004</v>
       </c>
       <c r="C332" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D332" s="28" t="s">
         <v>357</v>
@@ -17635,7 +17638,7 @@
     </row>
     <row r="333" spans="1:5" ht="14.25">
       <c r="A333" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B333" s="28">
         <v>2004</v>
@@ -17652,13 +17655,13 @@
     </row>
     <row r="334" spans="1:5" ht="14.25">
       <c r="A334" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B334" s="28">
         <v>2004</v>
       </c>
       <c r="C334" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D334" s="28" t="s">
         <v>355</v>
@@ -17669,13 +17672,13 @@
     </row>
     <row r="335" spans="1:5" ht="14.25">
       <c r="A335" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B335" s="28">
         <v>2004</v>
       </c>
       <c r="C335" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D335" s="28" t="s">
         <v>353</v>
@@ -17686,7 +17689,7 @@
     </row>
     <row r="336" spans="1:5" ht="14.25">
       <c r="A336" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B336" s="28">
         <v>2004</v>
@@ -17703,13 +17706,13 @@
     </row>
     <row r="337" spans="1:5" ht="14.25">
       <c r="A337" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B337" s="28">
         <v>2004</v>
       </c>
       <c r="C337" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D337" s="28" t="s">
         <v>356</v>
@@ -17720,7 +17723,7 @@
     </row>
     <row r="338" spans="1:5" ht="14.25">
       <c r="A338" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B338" s="28">
         <v>2004</v>
@@ -17737,13 +17740,13 @@
     </row>
     <row r="339" spans="1:5" ht="14.25">
       <c r="A339" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B339" s="28">
         <v>2004</v>
       </c>
       <c r="C339" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D339" s="28" t="s">
         <v>352</v>
@@ -17754,7 +17757,7 @@
     </row>
     <row r="340" spans="1:5" ht="14.25">
       <c r="A340" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B340" s="28">
         <v>2004</v>
@@ -17771,7 +17774,7 @@
     </row>
     <row r="341" spans="1:5" ht="14.25">
       <c r="A341" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B341" s="28">
         <v>2004</v>
@@ -17788,7 +17791,7 @@
     </row>
     <row r="342" spans="1:5" ht="14.25">
       <c r="A342" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B342" s="28">
         <v>2004</v>
@@ -17805,7 +17808,7 @@
     </row>
     <row r="343" spans="1:5" ht="14.25">
       <c r="A343" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B343" s="28">
         <v>2004</v>
@@ -17822,7 +17825,7 @@
     </row>
     <row r="344" spans="1:5" ht="14.25">
       <c r="A344" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B344" s="28">
         <v>2003</v>
@@ -17839,7 +17842,7 @@
     </row>
     <row r="345" spans="1:5" ht="14.25">
       <c r="A345" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B345" s="28">
         <v>2003</v>
@@ -17856,7 +17859,7 @@
     </row>
     <row r="346" spans="1:5" ht="14.25">
       <c r="A346" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B346" s="28">
         <v>2003</v>
@@ -17873,7 +17876,7 @@
     </row>
     <row r="347" spans="1:5" ht="14.25">
       <c r="A347" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B347" s="28">
         <v>2003</v>
@@ -17890,7 +17893,7 @@
     </row>
     <row r="348" spans="1:5" ht="14.25">
       <c r="A348" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B348" s="28">
         <v>2003</v>
@@ -17907,13 +17910,13 @@
     </row>
     <row r="349" spans="1:5" ht="14.25">
       <c r="A349" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B349" s="28">
         <v>2003</v>
       </c>
       <c r="C349" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D349" s="28" t="s">
         <v>354</v>
@@ -17924,13 +17927,13 @@
     </row>
     <row r="350" spans="1:5" ht="14.25">
       <c r="A350" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B350" s="28">
         <v>2003</v>
       </c>
       <c r="C350" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D350" s="28" t="s">
         <v>357</v>
@@ -17941,7 +17944,7 @@
     </row>
     <row r="351" spans="1:5" ht="14.25">
       <c r="A351" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B351" s="28">
         <v>2003</v>
@@ -17958,13 +17961,13 @@
     </row>
     <row r="352" spans="1:5" ht="14.25">
       <c r="A352" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B352" s="28">
         <v>2003</v>
       </c>
       <c r="C352" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D352" s="28" t="s">
         <v>355</v>
@@ -17975,13 +17978,13 @@
     </row>
     <row r="353" spans="1:5" ht="14.25">
       <c r="A353" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B353" s="28">
         <v>2003</v>
       </c>
       <c r="C353" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D353" s="28" t="s">
         <v>353</v>
@@ -17992,7 +17995,7 @@
     </row>
     <row r="354" spans="1:5" ht="14.25">
       <c r="A354" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B354" s="28">
         <v>2003</v>
@@ -18009,13 +18012,13 @@
     </row>
     <row r="355" spans="1:5" ht="14.25">
       <c r="A355" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B355" s="28">
         <v>2003</v>
       </c>
       <c r="C355" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D355" s="28" t="s">
         <v>356</v>
@@ -18026,7 +18029,7 @@
     </row>
     <row r="356" spans="1:5" ht="14.25">
       <c r="A356" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B356" s="28">
         <v>2003</v>
@@ -18043,7 +18046,7 @@
     </row>
     <row r="357" spans="1:5" ht="14.25">
       <c r="A357" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B357" s="28">
         <v>2003</v>
@@ -18060,7 +18063,7 @@
     </row>
     <row r="358" spans="1:5" ht="14.25">
       <c r="A358" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B358" s="28">
         <v>2003</v>
@@ -18077,7 +18080,7 @@
     </row>
     <row r="359" spans="1:5" ht="14.25">
       <c r="A359" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B359" s="28">
         <v>2003</v>
@@ -18094,13 +18097,13 @@
     </row>
     <row r="360" spans="1:5" ht="14.25">
       <c r="A360" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B360" s="28">
         <v>2003</v>
       </c>
       <c r="C360" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D360" s="28" t="s">
         <v>352</v>
@@ -18111,7 +18114,7 @@
     </row>
     <row r="361" spans="1:5" ht="14.25">
       <c r="A361" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B361" s="28">
         <v>2003</v>
@@ -18128,7 +18131,7 @@
     </row>
     <row r="362" spans="1:5" ht="14.25">
       <c r="A362" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B362" s="28">
         <v>2002</v>
@@ -18145,7 +18148,7 @@
     </row>
     <row r="363" spans="1:5" ht="14.25">
       <c r="A363" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B363" s="28">
         <v>2002</v>
@@ -18162,7 +18165,7 @@
     </row>
     <row r="364" spans="1:5" ht="14.25">
       <c r="A364" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B364" s="28">
         <v>2002</v>
@@ -18179,7 +18182,7 @@
     </row>
     <row r="365" spans="1:5" ht="14.25">
       <c r="A365" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B365" s="28">
         <v>2002</v>
@@ -18196,7 +18199,7 @@
     </row>
     <row r="366" spans="1:5" ht="14.25">
       <c r="A366" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B366" s="28">
         <v>2002</v>
@@ -18213,13 +18216,13 @@
     </row>
     <row r="367" spans="1:5" ht="14.25">
       <c r="A367" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B367" s="28">
         <v>2002</v>
       </c>
       <c r="C367" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D367" s="28" t="s">
         <v>354</v>
@@ -18230,13 +18233,13 @@
     </row>
     <row r="368" spans="1:5" ht="14.25">
       <c r="A368" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B368" s="28">
         <v>2002</v>
       </c>
       <c r="C368" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D368" s="28" t="s">
         <v>357</v>
@@ -18247,7 +18250,7 @@
     </row>
     <row r="369" spans="1:5" ht="14.25">
       <c r="A369" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B369" s="28">
         <v>2002</v>
@@ -18264,13 +18267,13 @@
     </row>
     <row r="370" spans="1:5" ht="14.25">
       <c r="A370" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B370" s="28">
         <v>2002</v>
       </c>
       <c r="C370" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D370" s="28" t="s">
         <v>355</v>
@@ -18281,7 +18284,7 @@
     </row>
     <row r="371" spans="1:5" ht="14.25">
       <c r="A371" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B371" s="28">
         <v>2002</v>
@@ -18298,13 +18301,13 @@
     </row>
     <row r="372" spans="1:5" ht="14.25">
       <c r="A372" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B372" s="28">
         <v>2002</v>
       </c>
       <c r="C372" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D372" s="28" t="s">
         <v>353</v>
@@ -18315,13 +18318,13 @@
     </row>
     <row r="373" spans="1:5" ht="14.25">
       <c r="A373" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B373" s="28">
         <v>2002</v>
       </c>
       <c r="C373" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D373" s="28" t="s">
         <v>356</v>
@@ -18332,7 +18335,7 @@
     </row>
     <row r="374" spans="1:5" ht="14.25">
       <c r="A374" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B374" s="28">
         <v>2002</v>
@@ -18349,7 +18352,7 @@
     </row>
     <row r="375" spans="1:5" ht="14.25">
       <c r="A375" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B375" s="28">
         <v>2002</v>
@@ -18366,7 +18369,7 @@
     </row>
     <row r="376" spans="1:5" ht="14.25">
       <c r="A376" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B376" s="28">
         <v>2002</v>
@@ -18383,7 +18386,7 @@
     </row>
     <row r="377" spans="1:5" ht="14.25">
       <c r="A377" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B377" s="28">
         <v>2002</v>
@@ -18400,13 +18403,13 @@
     </row>
     <row r="378" spans="1:5" ht="14.25">
       <c r="A378" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B378" s="28">
         <v>2002</v>
       </c>
       <c r="C378" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D378" s="28" t="s">
         <v>352</v>
@@ -18417,7 +18420,7 @@
     </row>
     <row r="379" spans="1:5" ht="14.25">
       <c r="A379" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B379" s="28">
         <v>2002</v>
@@ -18434,7 +18437,7 @@
     </row>
     <row r="380" spans="1:5" ht="14.25">
       <c r="A380" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B380" s="28">
         <v>2001</v>
@@ -18451,7 +18454,7 @@
     </row>
     <row r="381" spans="1:5" ht="14.25">
       <c r="A381" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B381" s="28">
         <v>2001</v>
@@ -18468,7 +18471,7 @@
     </row>
     <row r="382" spans="1:5" ht="14.25">
       <c r="A382" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B382" s="28">
         <v>2001</v>
@@ -18485,7 +18488,7 @@
     </row>
     <row r="383" spans="1:5" ht="14.25">
       <c r="A383" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B383" s="28">
         <v>2001</v>
@@ -18502,7 +18505,7 @@
     </row>
     <row r="384" spans="1:5" ht="14.25">
       <c r="A384" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B384" s="28">
         <v>2001</v>
@@ -18519,13 +18522,13 @@
     </row>
     <row r="385" spans="1:5" ht="14.25">
       <c r="A385" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B385" s="28">
         <v>2001</v>
       </c>
       <c r="C385" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D385" s="28" t="s">
         <v>354</v>
@@ -18536,7 +18539,7 @@
     </row>
     <row r="386" spans="1:5" ht="14.25">
       <c r="A386" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B386" s="28">
         <v>2001</v>
@@ -18553,13 +18556,13 @@
     </row>
     <row r="387" spans="1:5" ht="14.25">
       <c r="A387" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B387" s="28">
         <v>2001</v>
       </c>
       <c r="C387" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D387" s="28" t="s">
         <v>357</v>
@@ -18570,7 +18573,7 @@
     </row>
     <row r="388" spans="1:5" ht="14.25">
       <c r="A388" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B388" s="28">
         <v>2001</v>
@@ -18587,13 +18590,13 @@
     </row>
     <row r="389" spans="1:5" ht="14.25">
       <c r="A389" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B389" s="28">
         <v>2001</v>
       </c>
       <c r="C389" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D389" s="28" t="s">
         <v>355</v>
@@ -18604,7 +18607,7 @@
     </row>
     <row r="390" spans="1:5" ht="14.25">
       <c r="A390" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B390" s="28">
         <v>2001</v>
@@ -18621,13 +18624,13 @@
     </row>
     <row r="391" spans="1:5" ht="14.25">
       <c r="A391" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B391" s="28">
         <v>2001</v>
       </c>
       <c r="C391" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D391" s="28" t="s">
         <v>356</v>
@@ -18638,13 +18641,13 @@
     </row>
     <row r="392" spans="1:5" ht="14.25">
       <c r="A392" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B392" s="28">
         <v>2001</v>
       </c>
       <c r="C392" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D392" s="28" t="s">
         <v>353</v>
@@ -18655,7 +18658,7 @@
     </row>
     <row r="393" spans="1:5" ht="14.25">
       <c r="A393" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B393" s="28">
         <v>2001</v>
@@ -18672,7 +18675,7 @@
     </row>
     <row r="394" spans="1:5" ht="14.25">
       <c r="A394" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B394" s="28">
         <v>2001</v>
@@ -18689,7 +18692,7 @@
     </row>
     <row r="395" spans="1:5" ht="14.25">
       <c r="A395" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B395" s="28">
         <v>2001</v>
@@ -18706,7 +18709,7 @@
     </row>
     <row r="396" spans="1:5" ht="14.25">
       <c r="A396" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B396" s="28">
         <v>2001</v>
@@ -18723,13 +18726,13 @@
     </row>
     <row r="397" spans="1:5" ht="14.25">
       <c r="A397" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B397" s="28">
         <v>2001</v>
       </c>
       <c r="C397" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D397" s="28" t="s">
         <v>352</v>
@@ -18740,7 +18743,7 @@
     </row>
     <row r="398" spans="1:5" ht="14.25">
       <c r="A398" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B398" s="28">
         <v>2000</v>
@@ -18757,7 +18760,7 @@
     </row>
     <row r="399" spans="1:5" ht="14.25">
       <c r="A399" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B399" s="28">
         <v>2000</v>
@@ -18774,7 +18777,7 @@
     </row>
     <row r="400" spans="1:5" ht="14.25">
       <c r="A400" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B400" s="28">
         <v>2000</v>
@@ -18791,7 +18794,7 @@
     </row>
     <row r="401" spans="1:5" ht="14.25">
       <c r="A401" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B401" s="28">
         <v>2000</v>
@@ -18808,7 +18811,7 @@
     </row>
     <row r="402" spans="1:5" ht="14.25">
       <c r="A402" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B402" s="28">
         <v>2000</v>
@@ -18825,13 +18828,13 @@
     </row>
     <row r="403" spans="1:5" ht="14.25">
       <c r="A403" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B403" s="28">
         <v>2000</v>
       </c>
       <c r="C403" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D403" s="28" t="s">
         <v>354</v>
@@ -18842,7 +18845,7 @@
     </row>
     <row r="404" spans="1:5" ht="14.25">
       <c r="A404" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B404" s="28">
         <v>2000</v>
@@ -18859,13 +18862,13 @@
     </row>
     <row r="405" spans="1:5" ht="14.25">
       <c r="A405" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B405" s="28">
         <v>2000</v>
       </c>
       <c r="C405" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D405" s="28" t="s">
         <v>357</v>
@@ -18876,7 +18879,7 @@
     </row>
     <row r="406" spans="1:5" ht="14.25">
       <c r="A406" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B406" s="28">
         <v>2000</v>
@@ -18893,13 +18896,13 @@
     </row>
     <row r="407" spans="1:5" ht="14.25">
       <c r="A407" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B407" s="28">
         <v>2000</v>
       </c>
       <c r="C407" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D407" s="28" t="s">
         <v>355</v>
@@ -18910,7 +18913,7 @@
     </row>
     <row r="408" spans="1:5" ht="14.25">
       <c r="A408" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B408" s="28">
         <v>2000</v>
@@ -18927,13 +18930,13 @@
     </row>
     <row r="409" spans="1:5" ht="14.25">
       <c r="A409" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B409" s="28">
         <v>2000</v>
       </c>
       <c r="C409" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D409" s="28" t="s">
         <v>356</v>
@@ -18944,13 +18947,13 @@
     </row>
     <row r="410" spans="1:5" ht="14.25">
       <c r="A410" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B410" s="28">
         <v>2000</v>
       </c>
       <c r="C410" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D410" s="28" t="s">
         <v>353</v>
@@ -18961,7 +18964,7 @@
     </row>
     <row r="411" spans="1:5" ht="14.25">
       <c r="A411" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B411" s="28">
         <v>2000</v>
@@ -18978,7 +18981,7 @@
     </row>
     <row r="412" spans="1:5" ht="14.25">
       <c r="A412" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B412" s="28">
         <v>2000</v>
@@ -18995,7 +18998,7 @@
     </row>
     <row r="413" spans="1:5" ht="14.25">
       <c r="A413" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B413" s="28">
         <v>2000</v>
@@ -19012,7 +19015,7 @@
     </row>
     <row r="414" spans="1:5" ht="14.25">
       <c r="A414" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B414" s="28">
         <v>2000</v>
@@ -19029,13 +19032,13 @@
     </row>
     <row r="415" spans="1:5" ht="14.25">
       <c r="A415" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B415" s="28">
         <v>2000</v>
       </c>
       <c r="C415" s="28" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="D415" s="28" t="s">
         <v>352</v>
@@ -19300,7 +19303,7 @@
         <v>413</v>
       </c>
       <c r="B1" s="26" t="s">
-        <v>414</v>
+        <v>475</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -19308,15 +19311,15 @@
         <v>415</v>
       </c>
       <c r="B2" s="27" t="s">
-        <v>416</v>
+        <v>489</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="27" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B3" s="27" t="s">
-        <v>418</v>
+        <v>490</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -19324,31 +19327,31 @@
         <v>357</v>
       </c>
       <c r="B4" s="27" t="s">
-        <v>419</v>
+        <v>491</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="27" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>421</v>
+        <v>492</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="27" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="B6" s="27" t="s">
-        <v>423</v>
+        <v>493</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="25" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="B7" s="26" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -19361,7 +19364,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="27" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B9" s="27">
         <v>44</v>
@@ -19369,7 +19372,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="27" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="B10" s="27">
         <v>33</v>
@@ -19377,7 +19380,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="27" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="B11" s="27">
         <v>11</v>
@@ -19395,7 +19398,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="14.25">
       <c r="A1" s="25" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="B1" s="26" t="s">
         <v>494</v>
@@ -19404,12 +19407,12 @@
         <v>495</v>
       </c>
       <c r="D1" s="26" t="s">
-        <v>409</v>
+        <v>496</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="14.25">
       <c r="A2" s="27" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="B2" s="27">
         <v>0.2</v>
@@ -19423,7 +19426,7 @@
     </row>
     <row r="3" spans="1:4" ht="14.25">
       <c r="A3" s="27" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="B3" s="27">
         <v>4</v>
@@ -19437,15 +19440,15 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="25" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="B4" s="26" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="27" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="B5" s="27">
         <v>21</v>
@@ -19453,7 +19456,7 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="27" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="B6" s="27">
         <v>79</v>
@@ -24818,17 +24821,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="c8670835-afc4-4376-8ae0-1ffed5b27e6b" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b0bf4113-6f4a-4f3e-b5bb-503c4d9102e3">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010098970033F315F542A2D9640B7CC02236" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="94449e8ff35cec47b43afd2e381d9e90">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b0bf4113-6f4a-4f3e-b5bb-503c4d9102e3" xmlns:ns3="c8670835-afc4-4376-8ae0-1ffed5b27e6b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f7f21ad7dc1dad656b5a5a7699096a32" ns2:_="" ns3:_="">
     <xsd:import namespace="b0bf4113-6f4a-4f3e-b5bb-503c4d9102e3"/>
@@ -25069,6 +25061,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="c8670835-afc4-4376-8ae0-1ffed5b27e6b" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b0bf4113-6f4a-4f3e-b5bb-503c4d9102e3">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -25079,11 +25082,11 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF42F510-D400-4F69-838A-213F2CB9A7EF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA2588C5-0196-4360-8A98-A8906953FDD2}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA2588C5-0196-4360-8A98-A8906953FDD2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF42F510-D400-4F69-838A-213F2CB9A7EF}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
